--- a/data/Extra Grants_latest.xlsx
+++ b/data/Extra Grants_latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aphrcorg-my.sharepoint.com/personal/nnjenga_aphrc_org/Documents/CARTA Dashboard/ECRS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="13_ncr:1_{D015934C-5C8D-463B-9777-448ADC1EE7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C916BA-8656-4457-A29D-220595C8E40E}"/>
+  <xr:revisionPtr revIDLastSave="512" documentId="13_ncr:1_{D015934C-5C8D-463B-9777-448ADC1EE7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD65A88-CF7B-4379-88D6-88A30F94ED34}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="29" r:id="rId7"/>
+    <pivotCache cacheId="317" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -6327,36 +6327,6 @@
       <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -6394,6 +6364,36 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -14800,6 +14800,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -28310,7 +28313,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{551C2CDB-7398-421C-88CA-55BBA8F543FA}" name="PivotTable1" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{551C2CDB-7398-421C-88CA-55BBA8F543FA}" name="PivotTable1" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A5:E149" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29033,46 +29036,46 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AF8FCFC-489E-4F8D-895C-35AB7CBDA56C}" name="PivotTable11" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="13">
-  <location ref="B50:F63" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000002000000}" name="PivotTable3" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
+  <location ref="B7:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items count="35">
-        <item x="1"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="6"/>
-        <item x="18"/>
-        <item x="23"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="17"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="12"/>
+        <item h="1" x="6"/>
+        <item h="1" x="18"/>
+        <item h="1" x="23"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="5"/>
+        <item h="1" x="14"/>
+        <item h="1" x="20"/>
+        <item h="1" x="8"/>
+        <item h="1" x="11"/>
+        <item h="1" x="17"/>
         <item m="1" x="33"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="16"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="24"/>
-        <item m="1" x="32"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
+        <item h="1" x="9"/>
+        <item h="1" x="13"/>
+        <item h="1" x="19"/>
+        <item h="1" x="10"/>
+        <item h="1" x="15"/>
+        <item h="1" x="22"/>
+        <item h="1" x="7"/>
+        <item h="1" x="16"/>
+        <item h="1" x="21"/>
+        <item h="1" x="0"/>
+        <item h="1" x="24"/>
+        <item h="1" m="1" x="32"/>
+        <item h="1" x="25"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
         <item x="29"/>
         <item x="28"/>
-        <item x="30"/>
-        <item x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="31"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -29195,39 +29198,12 @@
   <rowFields count="1">
     <field x="16"/>
   </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
+  <rowItems count="3">
     <i>
       <x v="8"/>
     </i>
     <i>
       <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
@@ -29236,15 +29212,12 @@
   <colFields count="1">
     <field x="6"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="3">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -29257,7 +29230,7 @@
     <pageField fld="10" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
+    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="0" numFmtId="166"/>
   </dataFields>
   <formats count="2">
     <format dxfId="34">
@@ -29267,8 +29240,8 @@
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <conditionalFormats count="2">
-    <conditionalFormat priority="4">
+  <conditionalFormats count="1">
+    <conditionalFormat priority="6">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -29286,25 +29259,8 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="4" selected="0">
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
   </conditionalFormats>
-  <chartFormats count="13">
+  <chartFormats count="4">
     <chartFormat chart="2" format="6" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
@@ -29353,114 +29309,6 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="6" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -29475,7 +29323,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000003000000}" name="PivotTable4" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000003000000}" name="PivotTable4" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B5:F39" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29730,7 +29578,283 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000005000000}" name="PivotTable6" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A55:E68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="25">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="15">
+        <item x="5"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item m="1" x="13"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item m="1" x="29"/>
+        <item x="1"/>
+        <item m="1" x="30"/>
+        <item m="1" x="31"/>
+        <item m="1" x="24"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item m="1" x="27"/>
+        <item m="1" x="23"/>
+        <item m="1" x="32"/>
+        <item m="1" x="21"/>
+        <item m="1" x="25"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="2"/>
+        <item m="1" x="28"/>
+        <item m="1" x="26"/>
+        <item m="1" x="22"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item m="1" x="33"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="12">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="7"/>
+        <item h="1" m="1" x="8"/>
+        <item h="1" m="1" x="3"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" m="1" x="5"/>
+        <item h="1" m="1" x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="16"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="7" hier="-1"/>
+    <pageField fld="18" hier="-1"/>
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="2" numFmtId="1"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="55">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="59">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="61">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="16" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="64">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <conditionalFormats count="2">
+    <conditionalFormat priority="10">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="5">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="3" selected="0">
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000005000000}" name="PivotTable6" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A27:E29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29817,7 +29941,7 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="8" baseItem="5" numFmtId="166"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="64">
+    <format dxfId="54">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29833,8 +29957,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B407599-BB24-4523-B687-82A24A40E00E}" name="PivotTable3" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B407599-BB24-4523-B687-82A24A40E00E}" name="PivotTable3" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
   <location ref="A141:E156" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29983,7 +30107,7 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="8" baseItem="5" numFmtId="166"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="63">
+    <format dxfId="53">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -30037,8 +30161,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable2" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable2" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A82:B134" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -30479,35 +30603,35 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="2" baseItem="5"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="54">
+    <format dxfId="44">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="45">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="46">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="47">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="48">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="49">
       <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="16" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -30523,8 +30647,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000004000000}" name="PivotTable5" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="10">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000004000000}" name="PivotTable5" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="10">
   <location ref="A6:E19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -30751,14 +30875,29 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="52">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="43">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <conditionalFormats count="2">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="2" selected="0">
+              <x v="9"/>
+              <x v="10"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
     <conditionalFormat priority="4">
       <pivotAreas count="1">
         <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
@@ -30776,21 +30915,6 @@
               <x v="6"/>
               <x v="7"/>
               <x v="8"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="2" selected="0">
-              <x v="9"/>
-              <x v="10"/>
             </reference>
           </references>
         </pivotArea>
@@ -30886,12 +31010,432 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A55:E68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{518325C7-055A-4FD7-8A8B-DEB66D95FD13}" name="PivotTable1" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="22">
+  <location ref="B74:C78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item x="1"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="6"/>
+        <item x="18"/>
+        <item x="23"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item m="1" x="33"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="10"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="24"/>
+        <item m="1" x="32"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="15">
+        <item x="5"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item m="1" x="13"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item m="1" x="29"/>
+        <item x="1"/>
+        <item m="1" x="30"/>
+        <item m="1" x="31"/>
+        <item m="1" x="24"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item m="1" x="27"/>
+        <item m="1" x="23"/>
+        <item m="1" x="32"/>
+        <item m="1" x="21"/>
+        <item m="1" x="25"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="2"/>
+        <item m="1" x="28"/>
+        <item m="1" x="26"/>
+        <item m="1" x="22"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item m="1" x="33"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" sortType="ascending"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="7"/>
+        <item m="1" x="8"/>
+        <item m="1" x="3"/>
+        <item m="1" x="4"/>
+        <item m="1" x="5"/>
+        <item m="1" x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="4">
+    <pageField fld="7" hier="-1"/>
+    <pageField fld="1" hier="-1"/>
+    <pageField fld="18" hier="-1"/>
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="40">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="16">
+    <chartFormat chart="2" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AF8FCFC-489E-4F8D-895C-35AB7CBDA56C}" name="PivotTable11" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="13">
+  <location ref="B50:F63" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+  <pivotFields count="25">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item x="1"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="6"/>
+        <item x="18"/>
+        <item x="23"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="17"/>
+        <item m="1" x="33"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="10"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="24"/>
+        <item m="1" x="32"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -30970,14 +31514,14 @@
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending">
       <items count="12">
+        <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item x="0"/>
         <item x="6"/>
         <item x="7"/>
         <item x="8"/>
@@ -30992,12 +31536,12 @@
         <item x="2"/>
         <item x="1"/>
         <item x="0"/>
-        <item h="1" m="1" x="7"/>
-        <item h="1" m="1" x="8"/>
-        <item h="1" m="1" x="3"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" m="1" x="5"/>
-        <item h="1" m="1" x="6"/>
+        <item m="1" x="7"/>
+        <item m="1" x="8"/>
+        <item m="1" x="3"/>
+        <item m="1" x="4"/>
+        <item m="1" x="5"/>
+        <item m="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -31066,72 +31610,42 @@
       <x/>
     </i>
   </colItems>
-  <pageFields count="3">
+  <pageFields count="4">
     <pageField fld="7" hier="-1"/>
+    <pageField fld="1" hier="-1"/>
     <pageField fld="18" hier="-1"/>
     <pageField fld="10" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="2" numFmtId="1"/>
+    <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
   </dataFields>
-  <formats count="10">
-    <format dxfId="42">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
+  <formats count="2">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="46">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="48">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="16" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="49">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="51">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    <format dxfId="39">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <conditionalFormats count="2">
-    <conditionalFormat priority="5">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
             <reference field="4294967294" count="1" selected="0">
               <x v="0"/>
             </reference>
-            <reference field="16" count="3" selected="0">
-              <x v="5"/>
+            <reference field="16" count="4" selected="0">
               <x v="6"/>
               <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
             </reference>
           </references>
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="10">
+    <conditionalFormat priority="4">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -31139,17 +31653,175 @@
               <x v="0"/>
             </reference>
             <reference field="16" count="5">
-              <x v="0"/>
               <x v="1"/>
               <x v="2"/>
               <x v="3"/>
               <x v="4"/>
+              <x v="5"/>
             </reference>
           </references>
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
   </conditionalFormats>
+  <chartFormats count="13">
+    <chartFormat chart="2" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -31162,8 +31834,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0325BBC9-6471-430A-8157-D1A40160D7A8}" name="PivotTable10" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0325BBC9-6471-430A-8157-D1A40160D7A8}" name="PivotTable10" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
   <location ref="B28:E40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -31384,10 +32056,10 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="40">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -31473,683 +32145,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000002000000}" name="PivotTable3" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
-  <location ref="B7:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
-  <pivotFields count="25">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
-        <item h="1" x="12"/>
-        <item h="1" x="6"/>
-        <item h="1" x="18"/>
-        <item h="1" x="23"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="5"/>
-        <item h="1" x="14"/>
-        <item h="1" x="20"/>
-        <item h="1" x="8"/>
-        <item h="1" x="11"/>
-        <item h="1" x="17"/>
-        <item m="1" x="33"/>
-        <item h="1" x="9"/>
-        <item h="1" x="13"/>
-        <item h="1" x="19"/>
-        <item h="1" x="10"/>
-        <item h="1" x="15"/>
-        <item h="1" x="22"/>
-        <item h="1" x="7"/>
-        <item h="1" x="16"/>
-        <item h="1" x="21"/>
-        <item h="1" x="0"/>
-        <item h="1" x="24"/>
-        <item h="1" m="1" x="32"/>
-        <item h="1" x="25"/>
-        <item h="1" x="26"/>
-        <item h="1" x="27"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item h="1" x="30"/>
-        <item h="1" x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item m="1" x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="15">
-        <item x="5"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item m="1" x="13"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item m="1" x="29"/>
-        <item x="1"/>
-        <item m="1" x="30"/>
-        <item m="1" x="31"/>
-        <item m="1" x="24"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item m="1" x="27"/>
-        <item m="1" x="23"/>
-        <item m="1" x="32"/>
-        <item m="1" x="21"/>
-        <item m="1" x="25"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="2"/>
-        <item m="1" x="28"/>
-        <item m="1" x="26"/>
-        <item m="1" x="22"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item m="1" x="33"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="10">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item m="1" x="7"/>
-        <item m="1" x="8"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="16"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="6"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="4">
-    <pageField fld="7" hier="-1"/>
-    <pageField fld="1" hier="-1"/>
-    <pageField fld="18" hier="-1"/>
-    <pageField fld="10" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="38">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="39">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="6">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="5">
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <chartFormats count="4">
-    <chartFormat chart="2" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{518325C7-055A-4FD7-8A8B-DEB66D95FD13}" name="PivotTable1" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="22">
-  <location ref="B74:C78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
-  <pivotFields count="25">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item x="1"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="6"/>
-        <item x="18"/>
-        <item x="23"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="17"/>
-        <item m="1" x="33"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="16"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="24"/>
-        <item m="1" x="32"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item m="1" x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="15">
-        <item x="5"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item m="1" x="13"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item m="1" x="29"/>
-        <item x="1"/>
-        <item m="1" x="30"/>
-        <item m="1" x="31"/>
-        <item m="1" x="24"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item m="1" x="27"/>
-        <item m="1" x="23"/>
-        <item m="1" x="32"/>
-        <item m="1" x="21"/>
-        <item m="1" x="25"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="2"/>
-        <item m="1" x="28"/>
-        <item m="1" x="26"/>
-        <item m="1" x="22"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item m="1" x="33"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" sortType="ascending"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="10">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item m="1" x="7"/>
-        <item m="1" x="8"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="4">
-    <pageField fld="7" hier="-1"/>
-    <pageField fld="1" hier="-1"/>
-    <pageField fld="18" hier="-1"/>
-    <pageField fld="10" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="36">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="16">
-    <chartFormat chart="2" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:Y501" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:Y501" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="University of Malawi"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="18">
       <filters>
         <filter val="Graduate"/>
@@ -40330,7 +40328,7 @@
       <c r="X120" s="4"/>
       <c r="Y120" s="4"/>
     </row>
-    <row r="121" spans="1:25" hidden="1">
+    <row r="121" spans="1:25">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -43290,7 +43288,7 @@
       <c r="X167" s="4"/>
       <c r="Y167" s="4"/>
     </row>
-    <row r="168" spans="1:25" hidden="1">
+    <row r="168" spans="1:25">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -43352,7 +43350,7 @@
       <c r="X168" s="4"/>
       <c r="Y168" s="4"/>
     </row>
-    <row r="169" spans="1:25" hidden="1">
+    <row r="169" spans="1:25">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -43414,7 +43412,7 @@
       <c r="X169" s="4"/>
       <c r="Y169" s="4"/>
     </row>
-    <row r="170" spans="1:25" hidden="1">
+    <row r="170" spans="1:25">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -43476,7 +43474,7 @@
       <c r="X170" s="4"/>
       <c r="Y170" s="4"/>
     </row>
-    <row r="171" spans="1:25" hidden="1">
+    <row r="171" spans="1:25">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -43536,7 +43534,7 @@
       <c r="X171" s="4"/>
       <c r="Y171" s="4"/>
     </row>
-    <row r="172" spans="1:25" hidden="1">
+    <row r="172" spans="1:25">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -43598,7 +43596,7 @@
       <c r="X172" s="4"/>
       <c r="Y172" s="4"/>
     </row>
-    <row r="173" spans="1:25" hidden="1">
+    <row r="173" spans="1:25">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -43784,7 +43782,7 @@
       <c r="X175" s="4"/>
       <c r="Y175" s="4"/>
     </row>
-    <row r="176" spans="1:25" hidden="1">
+    <row r="176" spans="1:25">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -43842,7 +43840,7 @@
       <c r="X176" s="4"/>
       <c r="Y176" s="4"/>
     </row>
-    <row r="177" spans="1:25" hidden="1">
+    <row r="177" spans="1:25">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -43904,7 +43902,7 @@
       <c r="X177" s="4"/>
       <c r="Y177" s="4"/>
     </row>
-    <row r="178" spans="1:25" hidden="1">
+    <row r="178" spans="1:25">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -43966,7 +43964,7 @@
       <c r="X178" s="4"/>
       <c r="Y178" s="4"/>
     </row>
-    <row r="179" spans="1:25" hidden="1">
+    <row r="179" spans="1:25">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -44028,7 +44026,7 @@
       <c r="X179" s="4"/>
       <c r="Y179" s="4"/>
     </row>
-    <row r="180" spans="1:25" hidden="1">
+    <row r="180" spans="1:25">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -44090,7 +44088,7 @@
       <c r="X180" s="4"/>
       <c r="Y180" s="4"/>
     </row>
-    <row r="181" spans="1:25" hidden="1">
+    <row r="181" spans="1:25">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -44152,7 +44150,7 @@
       <c r="X181" s="4"/>
       <c r="Y181" s="4"/>
     </row>
-    <row r="182" spans="1:25" hidden="1">
+    <row r="182" spans="1:25">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -44214,7 +44212,7 @@
       <c r="X182" s="4"/>
       <c r="Y182" s="4"/>
     </row>
-    <row r="183" spans="1:25" hidden="1">
+    <row r="183" spans="1:25">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -44276,7 +44274,7 @@
       <c r="X183" s="4"/>
       <c r="Y183" s="4"/>
     </row>
-    <row r="184" spans="1:25" hidden="1">
+    <row r="184" spans="1:25">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -44338,7 +44336,7 @@
       <c r="X184" s="4"/>
       <c r="Y184" s="4"/>
     </row>
-    <row r="185" spans="1:25" hidden="1">
+    <row r="185" spans="1:25">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -44400,7 +44398,7 @@
       <c r="X185" s="4"/>
       <c r="Y185" s="4"/>
     </row>
-    <row r="186" spans="1:25" hidden="1">
+    <row r="186" spans="1:25">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -44456,7 +44454,7 @@
       <c r="X186" s="4"/>
       <c r="Y186" s="4"/>
     </row>
-    <row r="187" spans="1:25" hidden="1">
+    <row r="187" spans="1:25">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -44518,7 +44516,7 @@
       <c r="X187" s="4"/>
       <c r="Y187" s="4"/>
     </row>
-    <row r="188" spans="1:25" hidden="1">
+    <row r="188" spans="1:25">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -44580,7 +44578,7 @@
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
     </row>
-    <row r="189" spans="1:25" hidden="1">
+    <row r="189" spans="1:25">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -44642,7 +44640,7 @@
       <c r="X189" s="4"/>
       <c r="Y189" s="4"/>
     </row>
-    <row r="190" spans="1:25" hidden="1">
+    <row r="190" spans="1:25">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -44704,7 +44702,7 @@
       <c r="X190" s="4"/>
       <c r="Y190" s="4"/>
     </row>
-    <row r="191" spans="1:25" hidden="1">
+    <row r="191" spans="1:25">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -44760,7 +44758,7 @@
       <c r="X191" s="4"/>
       <c r="Y191" s="4"/>
     </row>
-    <row r="192" spans="1:25" hidden="1">
+    <row r="192" spans="1:25">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -44818,7 +44816,7 @@
       <c r="X192" s="4"/>
       <c r="Y192" s="4"/>
     </row>
-    <row r="193" spans="1:25" hidden="1">
+    <row r="193" spans="1:25">
       <c r="A193" s="3">
         <v>192</v>
       </c>
@@ -44878,7 +44876,7 @@
       <c r="X193" s="4"/>
       <c r="Y193" s="4"/>
     </row>
-    <row r="194" spans="1:25" hidden="1">
+    <row r="194" spans="1:25">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -44936,7 +44934,7 @@
       <c r="X194" s="4"/>
       <c r="Y194" s="4"/>
     </row>
-    <row r="195" spans="1:25" hidden="1">
+    <row r="195" spans="1:25">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -44994,7 +44992,7 @@
       <c r="X195" s="4"/>
       <c r="Y195" s="4"/>
     </row>
-    <row r="196" spans="1:25" hidden="1">
+    <row r="196" spans="1:25">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -45052,7 +45050,7 @@
       <c r="X196" s="4"/>
       <c r="Y196" s="4"/>
     </row>
-    <row r="197" spans="1:25" hidden="1">
+    <row r="197" spans="1:25">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -45114,7 +45112,7 @@
       <c r="X197" s="4"/>
       <c r="Y197" s="4"/>
     </row>
-    <row r="198" spans="1:25" hidden="1">
+    <row r="198" spans="1:25">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -45174,7 +45172,7 @@
       <c r="X198" s="4"/>
       <c r="Y198" s="4"/>
     </row>
-    <row r="199" spans="1:25" hidden="1">
+    <row r="199" spans="1:25">
       <c r="A199" s="3">
         <v>198</v>
       </c>
@@ -45236,7 +45234,7 @@
       <c r="X199" s="4"/>
       <c r="Y199" s="4"/>
     </row>
-    <row r="200" spans="1:25" hidden="1">
+    <row r="200" spans="1:25">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -45296,7 +45294,7 @@
       <c r="X200" s="4"/>
       <c r="Y200" s="4"/>
     </row>
-    <row r="201" spans="1:25" hidden="1">
+    <row r="201" spans="1:25">
       <c r="A201" s="3">
         <v>200</v>
       </c>
@@ -45416,7 +45414,7 @@
       <c r="X202" s="4"/>
       <c r="Y202" s="4"/>
     </row>
-    <row r="203" spans="1:25" hidden="1">
+    <row r="203" spans="1:25">
       <c r="A203" s="3">
         <v>202</v>
       </c>
@@ -45476,7 +45474,7 @@
       <c r="X203" s="4"/>
       <c r="Y203" s="4"/>
     </row>
-    <row r="204" spans="1:25" hidden="1">
+    <row r="204" spans="1:25">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -45724,7 +45722,7 @@
       <c r="X207" s="4"/>
       <c r="Y207" s="4"/>
     </row>
-    <row r="208" spans="1:25" hidden="1">
+    <row r="208" spans="1:25">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -45786,7 +45784,7 @@
       <c r="X208" s="4"/>
       <c r="Y208" s="4"/>
     </row>
-    <row r="209" spans="1:25" hidden="1">
+    <row r="209" spans="1:25">
       <c r="A209" s="3">
         <v>208</v>
       </c>
@@ -45846,7 +45844,7 @@
       <c r="X209" s="4"/>
       <c r="Y209" s="4"/>
     </row>
-    <row r="210" spans="1:25" hidden="1">
+    <row r="210" spans="1:25">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -45906,7 +45904,7 @@
       <c r="X210" s="4"/>
       <c r="Y210" s="4"/>
     </row>
-    <row r="211" spans="1:25" hidden="1">
+    <row r="211" spans="1:25">
       <c r="A211" s="3">
         <v>210</v>
       </c>
@@ -45968,7 +45966,7 @@
       <c r="X211" s="4"/>
       <c r="Y211" s="4"/>
     </row>
-    <row r="212" spans="1:25" hidden="1">
+    <row r="212" spans="1:25">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -46030,7 +46028,7 @@
       <c r="X212" s="4"/>
       <c r="Y212" s="4"/>
     </row>
-    <row r="213" spans="1:25" hidden="1">
+    <row r="213" spans="1:25">
       <c r="A213" s="3">
         <v>212</v>
       </c>
@@ -46092,7 +46090,7 @@
       <c r="X213" s="4"/>
       <c r="Y213" s="4"/>
     </row>
-    <row r="214" spans="1:25" hidden="1">
+    <row r="214" spans="1:25">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -46154,7 +46152,7 @@
       <c r="X214" s="4"/>
       <c r="Y214" s="4"/>
     </row>
-    <row r="215" spans="1:25" hidden="1">
+    <row r="215" spans="1:25">
       <c r="A215" s="3">
         <v>214</v>
       </c>
@@ -46214,7 +46212,7 @@
       <c r="X215" s="4"/>
       <c r="Y215" s="4"/>
     </row>
-    <row r="216" spans="1:25" hidden="1">
+    <row r="216" spans="1:25">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -46274,7 +46272,7 @@
       <c r="X216" s="4"/>
       <c r="Y216" s="4"/>
     </row>
-    <row r="217" spans="1:25" hidden="1">
+    <row r="217" spans="1:25">
       <c r="A217" s="3">
         <v>216</v>
       </c>
@@ -46334,7 +46332,7 @@
       <c r="X217" s="4"/>
       <c r="Y217" s="4"/>
     </row>
-    <row r="218" spans="1:25" hidden="1">
+    <row r="218" spans="1:25">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -47600,7 +47598,7 @@
       <c r="X237" s="4"/>
       <c r="Y237" s="4"/>
     </row>
-    <row r="238" spans="1:25" hidden="1">
+    <row r="238" spans="1:25">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -47662,7 +47660,7 @@
       <c r="X238" s="4"/>
       <c r="Y238" s="4"/>
     </row>
-    <row r="239" spans="1:25" hidden="1">
+    <row r="239" spans="1:25">
       <c r="A239" s="3">
         <v>238</v>
       </c>
@@ -47724,7 +47722,7 @@
       <c r="X239" s="4"/>
       <c r="Y239" s="4"/>
     </row>
-    <row r="240" spans="1:25" hidden="1">
+    <row r="240" spans="1:25">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -47852,7 +47850,7 @@
       <c r="X241" s="4"/>
       <c r="Y241" s="4"/>
     </row>
-    <row r="242" spans="1:25" hidden="1">
+    <row r="242" spans="1:25">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -47982,7 +47980,7 @@
       <c r="X243" s="4"/>
       <c r="Y243" s="4"/>
     </row>
-    <row r="244" spans="1:25" hidden="1">
+    <row r="244" spans="1:25">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -48044,7 +48042,7 @@
       <c r="X244" s="4"/>
       <c r="Y244" s="4"/>
     </row>
-    <row r="245" spans="1:25" hidden="1">
+    <row r="245" spans="1:25">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -48104,7 +48102,7 @@
       <c r="X245" s="4"/>
       <c r="Y245" s="4"/>
     </row>
-    <row r="246" spans="1:25" hidden="1">
+    <row r="246" spans="1:25">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -48164,7 +48162,7 @@
       <c r="X246" s="4"/>
       <c r="Y246" s="4"/>
     </row>
-    <row r="247" spans="1:25" hidden="1">
+    <row r="247" spans="1:25">
       <c r="A247" s="3">
         <v>246</v>
       </c>
@@ -49742,7 +49740,7 @@
       <c r="X271" s="4"/>
       <c r="Y271" s="4"/>
     </row>
-    <row r="272" spans="1:25" hidden="1">
+    <row r="272" spans="1:25">
       <c r="A272" s="3">
         <v>271</v>
       </c>
@@ -49802,7 +49800,7 @@
       <c r="X272" s="4"/>
       <c r="Y272" s="4"/>
     </row>
-    <row r="273" spans="1:25" hidden="1">
+    <row r="273" spans="1:25">
       <c r="A273" s="3">
         <v>272</v>
       </c>
@@ -49866,7 +49864,7 @@
       <c r="X273" s="4"/>
       <c r="Y273" s="4"/>
     </row>
-    <row r="274" spans="1:25" hidden="1">
+    <row r="274" spans="1:25">
       <c r="A274" s="3">
         <v>273</v>
       </c>
@@ -49928,7 +49926,7 @@
       <c r="X274" s="4"/>
       <c r="Y274" s="4"/>
     </row>
-    <row r="275" spans="1:25" hidden="1">
+    <row r="275" spans="1:25">
       <c r="A275" s="3">
         <v>274</v>
       </c>
@@ -49988,7 +49986,7 @@
       <c r="X275" s="4"/>
       <c r="Y275" s="4"/>
     </row>
-    <row r="276" spans="1:25" hidden="1">
+    <row r="276" spans="1:25">
       <c r="A276" s="3">
         <v>275</v>
       </c>
@@ -50050,7 +50048,7 @@
       <c r="X276" s="4"/>
       <c r="Y276" s="4"/>
     </row>
-    <row r="277" spans="1:25" hidden="1">
+    <row r="277" spans="1:25">
       <c r="A277" s="3">
         <v>276</v>
       </c>
@@ -50176,7 +50174,7 @@
       <c r="X278" s="4"/>
       <c r="Y278" s="4"/>
     </row>
-    <row r="279" spans="1:25" hidden="1">
+    <row r="279" spans="1:25">
       <c r="A279" s="3">
         <v>278</v>
       </c>
@@ -50238,7 +50236,7 @@
       <c r="X279" s="4"/>
       <c r="Y279" s="4"/>
     </row>
-    <row r="280" spans="1:25" hidden="1">
+    <row r="280" spans="1:25">
       <c r="A280" s="3">
         <v>279</v>
       </c>
@@ -50302,7 +50300,7 @@
       <c r="X280" s="4"/>
       <c r="Y280" s="4"/>
     </row>
-    <row r="281" spans="1:25" hidden="1">
+    <row r="281" spans="1:25">
       <c r="A281" s="3">
         <v>280</v>
       </c>
@@ -51256,7 +51254,7 @@
       <c r="X295" s="4"/>
       <c r="Y295" s="4"/>
     </row>
-    <row r="296" spans="1:25" hidden="1">
+    <row r="296" spans="1:25">
       <c r="A296" s="3">
         <v>295</v>
       </c>
@@ -51320,7 +51318,7 @@
       <c r="X296" s="4"/>
       <c r="Y296" s="4"/>
     </row>
-    <row r="297" spans="1:25" hidden="1">
+    <row r="297" spans="1:25">
       <c r="A297" s="3">
         <v>296</v>
       </c>
@@ -51384,7 +51382,7 @@
       <c r="X297" s="4"/>
       <c r="Y297" s="4"/>
     </row>
-    <row r="298" spans="1:25" hidden="1">
+    <row r="298" spans="1:25">
       <c r="A298" s="3">
         <v>297</v>
       </c>
@@ -51512,7 +51510,7 @@
       <c r="X299" s="4"/>
       <c r="Y299" s="4"/>
     </row>
-    <row r="300" spans="1:25" hidden="1">
+    <row r="300" spans="1:25">
       <c r="A300" s="3">
         <v>299</v>
       </c>
@@ -51572,7 +51570,7 @@
       <c r="X300" s="4"/>
       <c r="Y300" s="4"/>
     </row>
-    <row r="301" spans="1:25" hidden="1">
+    <row r="301" spans="1:25">
       <c r="A301" s="3">
         <v>300</v>
       </c>
@@ -51634,7 +51632,7 @@
       <c r="X301" s="4"/>
       <c r="Y301" s="4"/>
     </row>
-    <row r="302" spans="1:25" hidden="1">
+    <row r="302" spans="1:25">
       <c r="A302" s="3">
         <v>301</v>
       </c>
@@ -51696,7 +51694,7 @@
       <c r="X302" s="4"/>
       <c r="Y302" s="4"/>
     </row>
-    <row r="303" spans="1:25" hidden="1">
+    <row r="303" spans="1:25">
       <c r="A303" s="3">
         <v>302</v>
       </c>
@@ -51764,7 +51762,7 @@
       <c r="X303" s="4"/>
       <c r="Y303" s="4"/>
     </row>
-    <row r="304" spans="1:25" hidden="1">
+    <row r="304" spans="1:25">
       <c r="A304" s="3">
         <v>303</v>
       </c>
@@ -51828,7 +51826,7 @@
       <c r="X304" s="4"/>
       <c r="Y304" s="4"/>
     </row>
-    <row r="305" spans="1:25" hidden="1">
+    <row r="305" spans="1:25">
       <c r="A305" s="3">
         <v>304</v>
       </c>
@@ -51892,7 +51890,7 @@
       <c r="X305" s="4"/>
       <c r="Y305" s="4"/>
     </row>
-    <row r="306" spans="1:25" hidden="1">
+    <row r="306" spans="1:25">
       <c r="A306" s="3">
         <v>305</v>
       </c>
@@ -52900,7 +52898,7 @@
       <c r="X320" s="4"/>
       <c r="Y320" s="4"/>
     </row>
-    <row r="321" spans="1:25" hidden="1">
+    <row r="321" spans="1:25">
       <c r="A321" s="3">
         <v>320</v>
       </c>
@@ -52960,7 +52958,7 @@
       <c r="X321" s="4"/>
       <c r="Y321" s="4"/>
     </row>
-    <row r="322" spans="1:25" hidden="1">
+    <row r="322" spans="1:25">
       <c r="A322" s="3">
         <v>321</v>
       </c>
@@ -53022,7 +53020,7 @@
       <c r="X322" s="4"/>
       <c r="Y322" s="4"/>
     </row>
-    <row r="323" spans="1:25" hidden="1">
+    <row r="323" spans="1:25">
       <c r="A323" s="3">
         <v>322</v>
       </c>
@@ -53084,7 +53082,7 @@
       <c r="X323" s="4"/>
       <c r="Y323" s="4"/>
     </row>
-    <row r="324" spans="1:25" hidden="1">
+    <row r="324" spans="1:25">
       <c r="A324" s="3">
         <v>323</v>
       </c>
@@ -53148,7 +53146,7 @@
       <c r="X324" s="4"/>
       <c r="Y324" s="4"/>
     </row>
-    <row r="325" spans="1:25" hidden="1">
+    <row r="325" spans="1:25">
       <c r="A325" s="3">
         <v>324</v>
       </c>
@@ -53202,7 +53200,7 @@
       <c r="X325" s="4"/>
       <c r="Y325" s="4"/>
     </row>
-    <row r="326" spans="1:25" hidden="1">
+    <row r="326" spans="1:25">
       <c r="A326" s="3">
         <v>325</v>
       </c>
@@ -53264,7 +53262,7 @@
       <c r="X326" s="4"/>
       <c r="Y326" s="4"/>
     </row>
-    <row r="327" spans="1:25" hidden="1">
+    <row r="327" spans="1:25">
       <c r="A327" s="3">
         <v>326</v>
       </c>
@@ -53382,7 +53380,7 @@
       <c r="X328" s="4"/>
       <c r="Y328" s="4"/>
     </row>
-    <row r="329" spans="1:25" ht="14.45" hidden="1" customHeight="1">
+    <row r="329" spans="1:25" ht="14.45" customHeight="1">
       <c r="A329" s="3">
         <v>328</v>
       </c>
@@ -54334,7 +54332,7 @@
       <c r="X342" s="4"/>
       <c r="Y342" s="4"/>
     </row>
-    <row r="343" spans="1:25" hidden="1">
+    <row r="343" spans="1:25">
       <c r="A343" s="3">
         <v>342</v>
       </c>
@@ -54398,7 +54396,7 @@
       <c r="X343" s="4"/>
       <c r="Y343" s="4"/>
     </row>
-    <row r="344" spans="1:25" hidden="1">
+    <row r="344" spans="1:25">
       <c r="A344" s="3">
         <v>343</v>
       </c>
@@ -54464,7 +54462,7 @@
       <c r="X344" s="4"/>
       <c r="Y344" s="4"/>
     </row>
-    <row r="345" spans="1:25" hidden="1">
+    <row r="345" spans="1:25">
       <c r="A345" s="3">
         <v>344</v>
       </c>
@@ -54526,7 +54524,7 @@
       <c r="X345" s="4"/>
       <c r="Y345" s="4"/>
     </row>
-    <row r="346" spans="1:25" hidden="1">
+    <row r="346" spans="1:25">
       <c r="A346" s="3">
         <v>345</v>
       </c>
@@ -54588,7 +54586,7 @@
       <c r="X346" s="4"/>
       <c r="Y346" s="4"/>
     </row>
-    <row r="347" spans="1:25" hidden="1">
+    <row r="347" spans="1:25">
       <c r="A347" s="3">
         <v>346</v>
       </c>
@@ -54728,7 +54726,7 @@
       <c r="X348" s="4"/>
       <c r="Y348" s="4"/>
     </row>
-    <row r="349" spans="1:25" hidden="1">
+    <row r="349" spans="1:25">
       <c r="A349" s="3">
         <v>348</v>
       </c>
@@ -54798,7 +54796,7 @@
       <c r="X349" s="4"/>
       <c r="Y349" s="4"/>
     </row>
-    <row r="350" spans="1:25" hidden="1">
+    <row r="350" spans="1:25">
       <c r="A350" s="3">
         <v>349</v>
       </c>
@@ -55826,7 +55824,7 @@
       <c r="X364" s="4"/>
       <c r="Y364" s="4"/>
     </row>
-    <row r="365" spans="1:25" hidden="1">
+    <row r="365" spans="1:25">
       <c r="A365" s="3">
         <v>364</v>
       </c>
@@ -55894,7 +55892,7 @@
       </c>
       <c r="Y365" s="4"/>
     </row>
-    <row r="366" spans="1:25" hidden="1">
+    <row r="366" spans="1:25">
       <c r="A366" s="3">
         <v>365</v>
       </c>
@@ -55964,7 +55962,7 @@
       </c>
       <c r="Y366" s="4"/>
     </row>
-    <row r="367" spans="1:25" hidden="1">
+    <row r="367" spans="1:25">
       <c r="A367" s="3">
         <v>366</v>
       </c>
@@ -56032,7 +56030,7 @@
       <c r="X367" s="4"/>
       <c r="Y367" s="4"/>
     </row>
-    <row r="368" spans="1:25" hidden="1">
+    <row r="368" spans="1:25">
       <c r="A368" s="3">
         <v>367</v>
       </c>
@@ -56094,7 +56092,7 @@
       </c>
       <c r="Y368" s="4"/>
     </row>
-    <row r="369" spans="1:25" hidden="1">
+    <row r="369" spans="1:25">
       <c r="A369" s="3">
         <v>368</v>
       </c>
@@ -56156,7 +56154,7 @@
       </c>
       <c r="Y369" s="4"/>
     </row>
-    <row r="370" spans="1:25" hidden="1">
+    <row r="370" spans="1:25">
       <c r="A370" s="3">
         <v>369</v>
       </c>
@@ -56226,7 +56224,7 @@
       </c>
       <c r="Y370" s="4"/>
     </row>
-    <row r="371" spans="1:25" hidden="1">
+    <row r="371" spans="1:25">
       <c r="A371" s="3">
         <v>370</v>
       </c>
@@ -56298,7 +56296,7 @@
       </c>
       <c r="Y371" s="4"/>
     </row>
-    <row r="372" spans="1:25" hidden="1">
+    <row r="372" spans="1:25">
       <c r="A372" s="3">
         <v>371</v>
       </c>
@@ -56368,7 +56366,7 @@
       </c>
       <c r="Y372" s="4"/>
     </row>
-    <row r="373" spans="1:25" hidden="1">
+    <row r="373" spans="1:25">
       <c r="A373" s="3">
         <v>372</v>
       </c>
@@ -56438,7 +56436,7 @@
       </c>
       <c r="Y373" s="4"/>
     </row>
-    <row r="374" spans="1:25" hidden="1">
+    <row r="374" spans="1:25">
       <c r="A374" s="3">
         <v>373</v>
       </c>
@@ -56508,7 +56506,7 @@
       </c>
       <c r="Y374" s="4"/>
     </row>
-    <row r="375" spans="1:25" hidden="1">
+    <row r="375" spans="1:25">
       <c r="A375" s="3">
         <v>374</v>
       </c>
@@ -56578,7 +56576,7 @@
       </c>
       <c r="Y375" s="4"/>
     </row>
-    <row r="376" spans="1:25" hidden="1">
+    <row r="376" spans="1:25">
       <c r="A376" s="3">
         <v>375</v>
       </c>
@@ -56650,7 +56648,7 @@
       </c>
       <c r="Y376" s="4"/>
     </row>
-    <row r="377" spans="1:25" hidden="1">
+    <row r="377" spans="1:25">
       <c r="A377" s="3">
         <v>376</v>
       </c>
@@ -56714,7 +56712,7 @@
       </c>
       <c r="Y377" s="4"/>
     </row>
-    <row r="378" spans="1:25" hidden="1">
+    <row r="378" spans="1:25">
       <c r="A378" s="3">
         <v>377</v>
       </c>
@@ -57322,7 +57320,7 @@
       <c r="X386" s="18"/>
       <c r="Y386" s="4"/>
     </row>
-    <row r="387" spans="1:25" hidden="1">
+    <row r="387" spans="1:25">
       <c r="A387" s="3">
         <v>386</v>
       </c>
@@ -57390,7 +57388,7 @@
       </c>
       <c r="Y387" s="4"/>
     </row>
-    <row r="388" spans="1:25" hidden="1">
+    <row r="388" spans="1:25">
       <c r="A388" s="3">
         <v>387</v>
       </c>
@@ -57458,7 +57456,7 @@
       </c>
       <c r="Y388" s="4"/>
     </row>
-    <row r="389" spans="1:25" hidden="1">
+    <row r="389" spans="1:25">
       <c r="A389" s="3">
         <v>388</v>
       </c>
@@ -57526,7 +57524,7 @@
       </c>
       <c r="Y389" s="4"/>
     </row>
-    <row r="390" spans="1:25" hidden="1">
+    <row r="390" spans="1:25">
       <c r="A390" s="3">
         <v>389</v>
       </c>
@@ -57588,7 +57586,7 @@
       <c r="X390" s="4"/>
       <c r="Y390" s="4"/>
     </row>
-    <row r="391" spans="1:25" hidden="1">
+    <row r="391" spans="1:25">
       <c r="A391" s="3">
         <v>390</v>
       </c>
@@ -57656,7 +57654,7 @@
       </c>
       <c r="Y391" s="4"/>
     </row>
-    <row r="392" spans="1:25" hidden="1">
+    <row r="392" spans="1:25">
       <c r="A392" s="3">
         <v>391</v>
       </c>
@@ -57780,7 +57778,7 @@
       </c>
       <c r="Y393" s="4"/>
     </row>
-    <row r="394" spans="1:25" hidden="1">
+    <row r="394" spans="1:25">
       <c r="A394" s="3">
         <v>393</v>
       </c>
@@ -57842,7 +57840,7 @@
       <c r="X394" s="3"/>
       <c r="Y394" s="4"/>
     </row>
-    <row r="395" spans="1:25" hidden="1">
+    <row r="395" spans="1:25">
       <c r="A395" s="3">
         <v>394</v>
       </c>
@@ -57908,7 +57906,7 @@
       </c>
       <c r="Y395" s="4"/>
     </row>
-    <row r="396" spans="1:25" hidden="1">
+    <row r="396" spans="1:25">
       <c r="A396" s="3">
         <v>395</v>
       </c>
@@ -58550,7 +58548,7 @@
       <c r="X405" s="3"/>
       <c r="Y405" s="4"/>
     </row>
-    <row r="406" spans="1:25" hidden="1">
+    <row r="406" spans="1:25">
       <c r="A406" s="3">
         <v>405</v>
       </c>
@@ -58616,7 +58614,7 @@
       </c>
       <c r="Y406" s="4"/>
     </row>
-    <row r="407" spans="1:25" hidden="1">
+    <row r="407" spans="1:25">
       <c r="A407" s="3">
         <v>406</v>
       </c>
@@ -58682,7 +58680,7 @@
       </c>
       <c r="Y407" s="4"/>
     </row>
-    <row r="408" spans="1:25" hidden="1">
+    <row r="408" spans="1:25">
       <c r="A408" s="3">
         <v>407</v>
       </c>
@@ -58750,7 +58748,7 @@
       </c>
       <c r="Y408" s="4"/>
     </row>
-    <row r="409" spans="1:25" hidden="1">
+    <row r="409" spans="1:25">
       <c r="A409" s="3">
         <v>408</v>
       </c>
@@ -58818,7 +58816,7 @@
       </c>
       <c r="Y409" s="4"/>
     </row>
-    <row r="410" spans="1:25" hidden="1">
+    <row r="410" spans="1:25">
       <c r="A410" s="3">
         <v>409</v>
       </c>
@@ -58952,7 +58950,7 @@
       </c>
       <c r="Y411" s="4"/>
     </row>
-    <row r="412" spans="1:25" hidden="1">
+    <row r="412" spans="1:25">
       <c r="A412" s="3">
         <v>411</v>
       </c>
@@ -59018,7 +59016,7 @@
       </c>
       <c r="Y412" s="4"/>
     </row>
-    <row r="413" spans="1:25" hidden="1">
+    <row r="413" spans="1:25">
       <c r="A413" s="3">
         <v>412</v>
       </c>
@@ -59086,7 +59084,7 @@
       </c>
       <c r="Y413" s="4"/>
     </row>
-    <row r="414" spans="1:25" hidden="1">
+    <row r="414" spans="1:25">
       <c r="A414" s="3">
         <v>413</v>
       </c>
@@ -59150,7 +59148,7 @@
       </c>
       <c r="Y414" s="4"/>
     </row>
-    <row r="415" spans="1:25" hidden="1">
+    <row r="415" spans="1:25">
       <c r="A415" s="3">
         <v>414</v>
       </c>
@@ -59210,7 +59208,7 @@
       <c r="X415" s="3"/>
       <c r="Y415" s="4"/>
     </row>
-    <row r="416" spans="1:25" hidden="1">
+    <row r="416" spans="1:25">
       <c r="A416" s="3">
         <v>415</v>
       </c>
@@ -59420,7 +59418,7 @@
       </c>
       <c r="Y418" s="4"/>
     </row>
-    <row r="419" spans="1:25" hidden="1">
+    <row r="419" spans="1:25">
       <c r="A419" s="3">
         <v>418</v>
       </c>
@@ -59488,7 +59486,7 @@
       <c r="X419" s="18"/>
       <c r="Y419" s="4"/>
     </row>
-    <row r="420" spans="1:25" hidden="1">
+    <row r="420" spans="1:25">
       <c r="A420" s="3">
         <v>419</v>
       </c>
@@ -59556,7 +59554,7 @@
       </c>
       <c r="Y420" s="4"/>
     </row>
-    <row r="421" spans="1:25" hidden="1">
+    <row r="421" spans="1:25">
       <c r="A421" s="3">
         <v>420</v>
       </c>
@@ -59626,7 +59624,7 @@
       </c>
       <c r="Y421" s="4"/>
     </row>
-    <row r="422" spans="1:25" hidden="1">
+    <row r="422" spans="1:25">
       <c r="A422" s="3">
         <v>421</v>
       </c>
@@ -59696,7 +59694,7 @@
       </c>
       <c r="Y422" s="4"/>
     </row>
-    <row r="423" spans="1:25" hidden="1">
+    <row r="423" spans="1:25">
       <c r="A423" s="3">
         <v>422</v>
       </c>
@@ -59766,7 +59764,7 @@
       </c>
       <c r="Y423" s="4"/>
     </row>
-    <row r="424" spans="1:25" hidden="1">
+    <row r="424" spans="1:25">
       <c r="A424" s="3">
         <v>423</v>
       </c>
@@ -59836,7 +59834,7 @@
       </c>
       <c r="Y424" s="4"/>
     </row>
-    <row r="425" spans="1:25" hidden="1">
+    <row r="425" spans="1:25">
       <c r="A425" s="3">
         <v>424</v>
       </c>
@@ -59906,7 +59904,7 @@
       </c>
       <c r="Y425" s="4"/>
     </row>
-    <row r="426" spans="1:25" hidden="1">
+    <row r="426" spans="1:25">
       <c r="A426" s="3">
         <v>425</v>
       </c>
@@ -59976,7 +59974,7 @@
       </c>
       <c r="Y426" s="4"/>
     </row>
-    <row r="427" spans="1:25" hidden="1">
+    <row r="427" spans="1:25">
       <c r="A427" s="3">
         <v>426</v>
       </c>
@@ -60046,7 +60044,7 @@
       </c>
       <c r="Y427" s="4"/>
     </row>
-    <row r="428" spans="1:25" hidden="1">
+    <row r="428" spans="1:25">
       <c r="A428" s="3">
         <v>427</v>
       </c>
@@ -60116,7 +60114,7 @@
       </c>
       <c r="Y428" s="4"/>
     </row>
-    <row r="429" spans="1:25" hidden="1">
+    <row r="429" spans="1:25">
       <c r="A429" s="3">
         <v>428</v>
       </c>
@@ -60316,7 +60314,7 @@
       </c>
       <c r="Y431" s="4"/>
     </row>
-    <row r="432" spans="1:25" hidden="1">
+    <row r="432" spans="1:25">
       <c r="A432" s="3">
         <v>431</v>
       </c>
@@ -60382,7 +60380,7 @@
       <c r="X432" s="4"/>
       <c r="Y432" s="4"/>
     </row>
-    <row r="433" spans="1:25" hidden="1">
+    <row r="433" spans="1:25">
       <c r="A433" s="3">
         <v>432</v>
       </c>
@@ -60506,7 +60504,7 @@
       <c r="X434" s="4"/>
       <c r="Y434" s="4"/>
     </row>
-    <row r="435" spans="1:25" hidden="1">
+    <row r="435" spans="1:25">
       <c r="A435" s="3">
         <v>434</v>
       </c>
@@ -60560,7 +60558,7 @@
       <c r="X435" s="4"/>
       <c r="Y435" s="4"/>
     </row>
-    <row r="436" spans="1:25" hidden="1">
+    <row r="436" spans="1:25">
       <c r="A436" s="3">
         <v>435</v>
       </c>
@@ -60624,7 +60622,7 @@
       <c r="X436" s="4"/>
       <c r="Y436" s="4"/>
     </row>
-    <row r="437" spans="1:25" hidden="1">
+    <row r="437" spans="1:25">
       <c r="A437" s="3">
         <v>436</v>
       </c>
@@ -60688,7 +60686,7 @@
       <c r="X437" s="4"/>
       <c r="Y437" s="4"/>
     </row>
-    <row r="438" spans="1:25" hidden="1">
+    <row r="438" spans="1:25">
       <c r="A438" s="3">
         <v>437</v>
       </c>
@@ -60752,7 +60750,7 @@
       <c r="X438" s="4"/>
       <c r="Y438" s="4"/>
     </row>
-    <row r="439" spans="1:25" hidden="1">
+    <row r="439" spans="1:25">
       <c r="A439" s="3">
         <v>438</v>
       </c>
@@ -60816,7 +60814,7 @@
       <c r="X439" s="4"/>
       <c r="Y439" s="4"/>
     </row>
-    <row r="440" spans="1:25" hidden="1">
+    <row r="440" spans="1:25">
       <c r="A440" s="3">
         <v>439</v>
       </c>
@@ -60880,7 +60878,7 @@
       <c r="X440" s="4"/>
       <c r="Y440" s="4"/>
     </row>
-    <row r="441" spans="1:25" hidden="1">
+    <row r="441" spans="1:25">
       <c r="A441" s="3">
         <v>440</v>
       </c>
@@ -60944,7 +60942,7 @@
       <c r="X441" s="4"/>
       <c r="Y441" s="4"/>
     </row>
-    <row r="442" spans="1:25" hidden="1">
+    <row r="442" spans="1:25">
       <c r="A442" s="3">
         <v>441</v>
       </c>
@@ -61008,7 +61006,7 @@
       <c r="X442" s="4"/>
       <c r="Y442" s="4"/>
     </row>
-    <row r="443" spans="1:25" hidden="1">
+    <row r="443" spans="1:25">
       <c r="A443" s="3">
         <v>442</v>
       </c>
@@ -61072,7 +61070,7 @@
       <c r="X443" s="18"/>
       <c r="Y443" s="4"/>
     </row>
-    <row r="444" spans="1:25" hidden="1">
+    <row r="444" spans="1:25">
       <c r="A444" s="3">
         <v>443</v>
       </c>
@@ -61140,7 +61138,7 @@
       </c>
       <c r="Y444" s="4"/>
     </row>
-    <row r="445" spans="1:25" hidden="1">
+    <row r="445" spans="1:25">
       <c r="A445" s="3">
         <v>444</v>
       </c>
@@ -61206,7 +61204,7 @@
       <c r="X445" s="18"/>
       <c r="Y445" s="4"/>
     </row>
-    <row r="446" spans="1:25" hidden="1">
+    <row r="446" spans="1:25">
       <c r="A446" s="3">
         <v>445</v>
       </c>
@@ -61536,7 +61534,7 @@
       <c r="X450" s="3"/>
       <c r="Y450" s="4"/>
     </row>
-    <row r="451" spans="1:25" hidden="1">
+    <row r="451" spans="1:25">
       <c r="A451" s="3">
         <v>451</v>
       </c>
@@ -61602,7 +61600,7 @@
       <c r="X451" s="3"/>
       <c r="Y451" s="4"/>
     </row>
-    <row r="452" spans="1:25" hidden="1">
+    <row r="452" spans="1:25">
       <c r="A452" s="3">
         <v>452</v>
       </c>
@@ -61670,7 +61668,7 @@
       </c>
       <c r="Y452" s="4"/>
     </row>
-    <row r="453" spans="1:25" hidden="1">
+    <row r="453" spans="1:25">
       <c r="A453" s="3">
         <v>453</v>
       </c>
@@ -61726,7 +61724,7 @@
       <c r="X453" s="3"/>
       <c r="Y453" s="4"/>
     </row>
-    <row r="454" spans="1:25" hidden="1">
+    <row r="454" spans="1:25">
       <c r="A454" s="3">
         <v>454</v>
       </c>
@@ -61794,7 +61792,7 @@
       </c>
       <c r="Y454" s="4"/>
     </row>
-    <row r="455" spans="1:25" hidden="1">
+    <row r="455" spans="1:25">
       <c r="A455" s="3">
         <v>455</v>
       </c>
@@ -61856,7 +61854,7 @@
       </c>
       <c r="Y455" s="4"/>
     </row>
-    <row r="456" spans="1:25" hidden="1">
+    <row r="456" spans="1:25">
       <c r="A456" s="3">
         <v>456</v>
       </c>
@@ -61920,7 +61918,7 @@
       </c>
       <c r="Y456" s="4"/>
     </row>
-    <row r="457" spans="1:25" hidden="1">
+    <row r="457" spans="1:25">
       <c r="A457" s="3">
         <v>457</v>
       </c>
@@ -61986,7 +61984,7 @@
       </c>
       <c r="Y457" s="4"/>
     </row>
-    <row r="458" spans="1:25" hidden="1">
+    <row r="458" spans="1:25">
       <c r="A458" s="3">
         <v>458</v>
       </c>
@@ -62050,7 +62048,7 @@
       </c>
       <c r="Y458" s="4"/>
     </row>
-    <row r="459" spans="1:25" hidden="1">
+    <row r="459" spans="1:25">
       <c r="A459" s="3">
         <v>459</v>
       </c>
@@ -62118,7 +62116,7 @@
       </c>
       <c r="Y459" s="4"/>
     </row>
-    <row r="460" spans="1:25" hidden="1">
+    <row r="460" spans="1:25">
       <c r="A460" s="3">
         <v>460</v>
       </c>
@@ -62182,7 +62180,7 @@
       </c>
       <c r="Y460" s="4"/>
     </row>
-    <row r="461" spans="1:25" hidden="1">
+    <row r="461" spans="1:25">
       <c r="A461" s="3">
         <v>461</v>
       </c>
@@ -62248,7 +62246,7 @@
       <c r="X461" s="18"/>
       <c r="Y461" s="4"/>
     </row>
-    <row r="462" spans="1:25" hidden="1">
+    <row r="462" spans="1:25">
       <c r="A462" s="3">
         <v>462</v>
       </c>
@@ -62318,7 +62316,7 @@
       <c r="X462" s="18"/>
       <c r="Y462" s="4"/>
     </row>
-    <row r="463" spans="1:25" hidden="1">
+    <row r="463" spans="1:25">
       <c r="A463" s="3">
         <v>463</v>
       </c>
@@ -62386,7 +62384,7 @@
       <c r="X463" s="18"/>
       <c r="Y463" s="4"/>
     </row>
-    <row r="464" spans="1:25" hidden="1">
+    <row r="464" spans="1:25">
       <c r="A464" s="3">
         <v>464</v>
       </c>
@@ -62454,7 +62452,7 @@
       <c r="X464" s="4"/>
       <c r="Y464" s="4"/>
     </row>
-    <row r="465" spans="1:25" ht="12.75" hidden="1" customHeight="1">
+    <row r="465" spans="1:25" ht="12.75" customHeight="1">
       <c r="A465" s="3">
         <v>465</v>
       </c>
@@ -62518,7 +62516,7 @@
       </c>
       <c r="Y465" s="4"/>
     </row>
-    <row r="466" spans="1:25" hidden="1">
+    <row r="466" spans="1:25">
       <c r="A466" s="3">
         <v>466</v>
       </c>
@@ -62586,7 +62584,7 @@
       </c>
       <c r="Y466" s="4"/>
     </row>
-    <row r="467" spans="1:25" hidden="1">
+    <row r="467" spans="1:25">
       <c r="A467" s="3">
         <v>467</v>
       </c>
@@ -62726,7 +62724,7 @@
       </c>
       <c r="Y468" s="4"/>
     </row>
-    <row r="469" spans="1:25" hidden="1">
+    <row r="469" spans="1:25">
       <c r="A469" s="3">
         <v>469</v>
       </c>
@@ -62796,7 +62794,7 @@
       </c>
       <c r="Y469" s="4"/>
     </row>
-    <row r="470" spans="1:25" hidden="1">
+    <row r="470" spans="1:25">
       <c r="A470" s="3">
         <v>470</v>
       </c>
@@ -62860,7 +62858,7 @@
       <c r="X470" s="18"/>
       <c r="Y470" s="4"/>
     </row>
-    <row r="471" spans="1:25" hidden="1">
+    <row r="471" spans="1:25">
       <c r="A471" s="3">
         <v>471</v>
       </c>
@@ -63132,7 +63130,7 @@
       </c>
       <c r="Y474" s="4"/>
     </row>
-    <row r="475" spans="1:25" hidden="1">
+    <row r="475" spans="1:25">
       <c r="A475" s="3">
         <v>475</v>
       </c>
@@ -63198,7 +63196,7 @@
       </c>
       <c r="Y475" s="4"/>
     </row>
-    <row r="476" spans="1:25" hidden="1">
+    <row r="476" spans="1:25">
       <c r="A476" s="3">
         <v>476</v>
       </c>
@@ -63268,7 +63266,7 @@
       </c>
       <c r="Y476" s="4"/>
     </row>
-    <row r="477" spans="1:25" hidden="1">
+    <row r="477" spans="1:25">
       <c r="A477" s="3">
         <v>477</v>
       </c>
@@ -63336,7 +63334,7 @@
       </c>
       <c r="Y477" s="4"/>
     </row>
-    <row r="478" spans="1:25" hidden="1">
+    <row r="478" spans="1:25">
       <c r="A478" s="3">
         <v>478</v>
       </c>
@@ -63546,7 +63544,7 @@
       <c r="X480" s="57"/>
       <c r="Y480" s="18"/>
     </row>
-    <row r="481" spans="1:25" hidden="1">
+    <row r="481" spans="1:25">
       <c r="A481" s="3">
         <v>481</v>
       </c>
@@ -63616,7 +63614,7 @@
       </c>
       <c r="Y481" s="4"/>
     </row>
-    <row r="482" spans="1:25" hidden="1">
+    <row r="482" spans="1:25">
       <c r="A482" s="3">
         <v>482</v>
       </c>
@@ -63684,7 +63682,7 @@
       </c>
       <c r="Y482" s="4"/>
     </row>
-    <row r="483" spans="1:25" hidden="1">
+    <row r="483" spans="1:25">
       <c r="A483" s="3">
         <v>483</v>
       </c>
@@ -63750,7 +63748,7 @@
       </c>
       <c r="Y483" s="4"/>
     </row>
-    <row r="484" spans="1:25" hidden="1">
+    <row r="484" spans="1:25">
       <c r="A484" s="3">
         <v>484</v>
       </c>
@@ -63818,7 +63816,7 @@
       <c r="X484" s="3"/>
       <c r="Y484" s="4"/>
     </row>
-    <row r="485" spans="1:25" hidden="1">
+    <row r="485" spans="1:25">
       <c r="A485" s="3">
         <v>485</v>
       </c>
@@ -63884,7 +63882,7 @@
       </c>
       <c r="Y485" s="4"/>
     </row>
-    <row r="486" spans="1:25" hidden="1">
+    <row r="486" spans="1:25">
       <c r="A486" s="3">
         <v>486</v>
       </c>
@@ -63954,7 +63952,7 @@
       </c>
       <c r="Y486" s="4"/>
     </row>
-    <row r="487" spans="1:25" hidden="1">
+    <row r="487" spans="1:25">
       <c r="A487" s="3">
         <v>487</v>
       </c>
@@ -64022,7 +64020,7 @@
       </c>
       <c r="Y487" s="4"/>
     </row>
-    <row r="488" spans="1:25" hidden="1">
+    <row r="488" spans="1:25">
       <c r="A488" s="3">
         <v>488</v>
       </c>
@@ -64088,7 +64086,7 @@
       </c>
       <c r="Y488" s="4"/>
     </row>
-    <row r="489" spans="1:25" hidden="1">
+    <row r="489" spans="1:25">
       <c r="A489" s="3">
         <v>489</v>
       </c>
@@ -64154,7 +64152,7 @@
       </c>
       <c r="Y489" s="4"/>
     </row>
-    <row r="490" spans="1:25" hidden="1">
+    <row r="490" spans="1:25">
       <c r="A490" s="3">
         <v>490</v>
       </c>
@@ -64224,7 +64222,7 @@
       </c>
       <c r="Y490" s="18"/>
     </row>
-    <row r="491" spans="1:25" hidden="1">
+    <row r="491" spans="1:25">
       <c r="A491" s="3">
         <v>491</v>
       </c>
@@ -64292,7 +64290,7 @@
       </c>
       <c r="Y491" s="4"/>
     </row>
-    <row r="492" spans="1:25" hidden="1">
+    <row r="492" spans="1:25">
       <c r="A492" s="3">
         <v>492</v>
       </c>
@@ -64360,7 +64358,7 @@
       </c>
       <c r="Y492" s="4"/>
     </row>
-    <row r="493" spans="1:25" hidden="1">
+    <row r="493" spans="1:25">
       <c r="A493" s="3">
         <v>493</v>
       </c>
@@ -64496,7 +64494,7 @@
       </c>
       <c r="Y494" s="4"/>
     </row>
-    <row r="495" spans="1:25" hidden="1">
+    <row r="495" spans="1:25">
       <c r="A495" s="3">
         <v>495</v>
       </c>
@@ -64564,7 +64562,7 @@
       </c>
       <c r="Y495" s="18"/>
     </row>
-    <row r="496" spans="1:25" hidden="1">
+    <row r="496" spans="1:25">
       <c r="A496" s="3">
         <v>496</v>
       </c>
@@ -64914,7 +64912,7 @@
       </c>
       <c r="Y500" s="18"/>
     </row>
-    <row r="501" spans="1:25" hidden="1">
+    <row r="501" spans="1:25">
       <c r="A501" s="3">
         <v>501</v>
       </c>

--- a/data/Extra Grants_latest.xlsx
+++ b/data/Extra Grants_latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aphrcorg-my.sharepoint.com/personal/nnjenga_aphrc_org/Documents/CARTA Dashboard/ECRS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="512" documentId="13_ncr:1_{D015934C-5C8D-463B-9777-448ADC1EE7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD65A88-CF7B-4379-88D6-88A30F94ED34}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="13_ncr:1_{D015934C-5C8D-463B-9777-448ADC1EE7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE896340-0B1E-4C54-97FE-CE02BA919214}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="317" r:id="rId7"/>
+    <pivotCache cacheId="210" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -6327,7 +6327,7 @@
       <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -6360,13 +6360,13 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -28313,7 +28313,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{551C2CDB-7398-421C-88CA-55BBA8F543FA}" name="PivotTable1" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{551C2CDB-7398-421C-88CA-55BBA8F543FA}" name="PivotTable1" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A5:E149" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29036,46 +29036,46 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000002000000}" name="PivotTable3" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
-  <location ref="B7:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0325BBC9-6471-430A-8157-D1A40160D7A8}" name="PivotTable10" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
+  <location ref="B28:E40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items count="35">
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
-        <item h="1" x="12"/>
-        <item h="1" x="6"/>
-        <item h="1" x="18"/>
-        <item h="1" x="23"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="5"/>
-        <item h="1" x="14"/>
-        <item h="1" x="20"/>
-        <item h="1" x="8"/>
-        <item h="1" x="11"/>
-        <item h="1" x="17"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="6"/>
+        <item x="18"/>
+        <item x="23"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="17"/>
         <item m="1" x="33"/>
-        <item h="1" x="9"/>
-        <item h="1" x="13"/>
-        <item h="1" x="19"/>
-        <item h="1" x="10"/>
-        <item h="1" x="15"/>
-        <item h="1" x="22"/>
-        <item h="1" x="7"/>
-        <item h="1" x="16"/>
-        <item h="1" x="21"/>
-        <item h="1" x="0"/>
-        <item h="1" x="24"/>
-        <item h="1" m="1" x="32"/>
-        <item h="1" x="25"/>
-        <item h="1" x="26"/>
-        <item h="1" x="27"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="10"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="24"/>
+        <item m="1" x="32"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
         <item x="29"/>
         <item x="28"/>
-        <item h="1" x="30"/>
-        <item h="1" x="31"/>
+        <item x="30"/>
+        <item x="31"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -29176,9 +29176,9 @@
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items count="10">
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item x="1"/>
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item m="1" x="7"/>
         <item m="1" x="8"/>
         <item m="1" x="3"/>
@@ -29198,12 +29198,36 @@
   <rowFields count="1">
     <field x="16"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="11">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
     <i>
       <x v="8"/>
     </i>
     <i>
       <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
@@ -29230,7 +29254,7 @@
     <pageField fld="10" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="0" numFmtId="166"/>
+    <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
   </dataFields>
   <formats count="2">
     <format dxfId="34">
@@ -29241,7 +29265,7 @@
     </format>
   </formats>
   <conditionalFormats count="1">
-    <conditionalFormat priority="6">
+    <conditionalFormat priority="5">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -29323,7 +29347,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000003000000}" name="PivotTable4" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000003000000}" name="PivotTable4" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B5:F39" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29578,591 +29602,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A55:E68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
-  <pivotFields count="25">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item m="1" x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="15">
-        <item x="5"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item m="1" x="13"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item m="1" x="29"/>
-        <item x="1"/>
-        <item m="1" x="30"/>
-        <item m="1" x="31"/>
-        <item m="1" x="24"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item m="1" x="27"/>
-        <item m="1" x="23"/>
-        <item m="1" x="32"/>
-        <item m="1" x="21"/>
-        <item m="1" x="25"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="2"/>
-        <item m="1" x="28"/>
-        <item m="1" x="26"/>
-        <item m="1" x="22"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item m="1" x="33"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="12">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="10">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item h="1" m="1" x="7"/>
-        <item h="1" m="1" x="8"/>
-        <item h="1" m="1" x="3"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" m="1" x="5"/>
-        <item h="1" m="1" x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="16"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="6"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="3">
-    <pageField fld="7" hier="-1"/>
-    <pageField fld="18" hier="-1"/>
-    <pageField fld="10" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="2" numFmtId="1"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="55">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="56">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="57">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="58">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="59">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="60">
-      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="61">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="16" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="62">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="63">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="64">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <conditionalFormats count="2">
-    <conditionalFormat priority="10">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="5">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="5">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="3" selected="0">
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000005000000}" name="PivotTable6" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A27:E29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="25">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item m="1" x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="20">
-        <item x="1"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item m="1" x="14"/>
-        <item m="1" x="15"/>
-        <item m="1" x="16"/>
-        <item m="1" x="17"/>
-        <item m="1" x="18"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="6"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="15" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Total amount in $" fld="12" baseField="8" baseItem="5" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="54">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B407599-BB24-4523-B687-82A24A40E00E}" name="PivotTable3" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
-  <location ref="A141:E156" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="25">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item m="1" x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="15">
-        <item x="5"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item m="1" x="13"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="20">
-        <item x="1"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item m="1" x="14"/>
-        <item m="1" x="15"/>
-        <item m="1" x="16"/>
-        <item m="1" x="17"/>
-        <item m="1" x="18"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="6"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="15" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Total amount in $" fld="12" baseField="8" baseItem="5" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="53">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="3">
-    <chartFormat chart="5" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable2" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable2" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A82:B134" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -30603,35 +30043,35 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="2" baseItem="5"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="44">
+    <format dxfId="56">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="57">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="58">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="59">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="60">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="61">
       <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="16" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -30647,8 +30087,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000004000000}" name="PivotTable5" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="10">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000004000000}" name="PivotTable5" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="10">
   <location ref="A6:E19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -30875,29 +30315,14 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="42">
+    <format dxfId="54">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="55">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <conditionalFormats count="2">
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="2" selected="0">
-              <x v="9"/>
-              <x v="10"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
     <conditionalFormat priority="4">
       <pivotAreas count="1">
         <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
@@ -30915,6 +30340,21 @@
               <x v="6"/>
               <x v="7"/>
               <x v="8"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="2" selected="0">
+              <x v="9"/>
+              <x v="10"/>
             </reference>
           </references>
         </pivotArea>
@@ -31010,8 +30450,879 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A55:E68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="25">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="15">
+        <item x="5"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item m="1" x="13"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item m="1" x="29"/>
+        <item x="1"/>
+        <item m="1" x="30"/>
+        <item m="1" x="31"/>
+        <item m="1" x="24"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item m="1" x="27"/>
+        <item m="1" x="23"/>
+        <item m="1" x="32"/>
+        <item m="1" x="21"/>
+        <item m="1" x="25"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="2"/>
+        <item m="1" x="28"/>
+        <item m="1" x="26"/>
+        <item m="1" x="22"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item m="1" x="33"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="12">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item h="1" m="1" x="7"/>
+        <item h="1" m="1" x="8"/>
+        <item h="1" m="1" x="3"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" m="1" x="5"/>
+        <item h="1" m="1" x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="16"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="7" hier="-1"/>
+    <pageField fld="18" hier="-1"/>
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="2" numFmtId="1"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="44">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="49">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="16" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="51">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="53">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <conditionalFormats count="2">
+    <conditionalFormat priority="5">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="3" selected="0">
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="10">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000005000000}" name="PivotTable6" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A27:E29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="25">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="20">
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
+        <item m="1" x="16"/>
+        <item m="1" x="17"/>
+        <item m="1" x="18"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="15" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Total amount in $" fld="12" baseField="8" baseItem="5" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="43">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B407599-BB24-4523-B687-82A24A40E00E}" name="PivotTable3" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A141:E156" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="25">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="15">
+        <item x="5"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item m="1" x="13"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="20">
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
+        <item m="1" x="16"/>
+        <item m="1" x="17"/>
+        <item m="1" x="18"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="15" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Total amount in $" fld="12" baseField="8" baseItem="5" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="42">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="5" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{518325C7-055A-4FD7-8A8B-DEB66D95FD13}" name="PivotTable1" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="22">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000002000000}" name="PivotTable3" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
+  <location ref="B7:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+  <pivotFields count="25">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="12"/>
+        <item h="1" x="6"/>
+        <item h="1" x="18"/>
+        <item h="1" x="23"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="5"/>
+        <item h="1" x="14"/>
+        <item h="1" x="20"/>
+        <item h="1" x="8"/>
+        <item h="1" x="11"/>
+        <item h="1" x="17"/>
+        <item m="1" x="33"/>
+        <item h="1" x="9"/>
+        <item h="1" x="13"/>
+        <item h="1" x="19"/>
+        <item h="1" x="10"/>
+        <item h="1" x="15"/>
+        <item h="1" x="22"/>
+        <item h="1" x="7"/>
+        <item h="1" x="16"/>
+        <item h="1" x="21"/>
+        <item h="1" x="0"/>
+        <item h="1" x="24"/>
+        <item h="1" m="1" x="32"/>
+        <item h="1" x="25"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item h="1" x="30"/>
+        <item h="1" x="31"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item m="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="15">
+        <item x="5"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item m="1" x="13"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item m="1" x="29"/>
+        <item x="1"/>
+        <item m="1" x="30"/>
+        <item m="1" x="31"/>
+        <item m="1" x="24"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item m="1" x="27"/>
+        <item m="1" x="23"/>
+        <item m="1" x="32"/>
+        <item m="1" x="21"/>
+        <item m="1" x="25"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="2"/>
+        <item m="1" x="28"/>
+        <item m="1" x="26"/>
+        <item m="1" x="22"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item m="1" x="33"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="7"/>
+        <item m="1" x="8"/>
+        <item m="1" x="3"/>
+        <item m="1" x="4"/>
+        <item m="1" x="5"/>
+        <item m="1" x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="16"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="4">
+    <pageField fld="7" hier="-1"/>
+    <pageField fld="1" hier="-1"/>
+    <pageField fld="18" hier="-1"/>
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Total amount in $" fld="12" subtotal="count" baseField="16" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="40">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="6">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="5">
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <chartFormats count="4">
+    <chartFormat chart="2" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{518325C7-055A-4FD7-8A8B-DEB66D95FD13}" name="PivotTable1" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="22">
   <location ref="B74:C78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -31185,10 +31496,10 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="40">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -31392,8 +31703,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AF8FCFC-489E-4F8D-895C-35AB7CBDA56C}" name="PivotTable11" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="13">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AF8FCFC-489E-4F8D-895C-35AB7CBDA56C}" name="PivotTable11" cacheId="210" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="13">
   <location ref="B50:F63" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -31620,31 +31931,14 @@
     <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="38">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <conditionalFormats count="2">
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="4" selected="0">
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
     <conditionalFormat priority="4">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
@@ -31658,6 +31952,23 @@
               <x v="3"/>
               <x v="4"/>
               <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="16" count="4" selected="0">
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
             </reference>
           </references>
         </pivotArea>
@@ -31834,323 +32145,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0325BBC9-6471-430A-8157-D1A40160D7A8}" name="PivotTable10" cacheId="317" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showMissing="0" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
-  <location ref="B28:E40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
-  <pivotFields count="25">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item x="1"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="6"/>
-        <item x="18"/>
-        <item x="23"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="17"/>
-        <item m="1" x="33"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="16"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="24"/>
-        <item m="1" x="32"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item m="1" x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="15">
-        <item x="5"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item m="1" x="13"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item m="1" x="29"/>
-        <item x="1"/>
-        <item m="1" x="30"/>
-        <item m="1" x="31"/>
-        <item m="1" x="24"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item m="1" x="27"/>
-        <item m="1" x="23"/>
-        <item m="1" x="32"/>
-        <item m="1" x="21"/>
-        <item m="1" x="25"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="2"/>
-        <item m="1" x="28"/>
-        <item m="1" x="26"/>
-        <item m="1" x="22"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item m="1" x="33"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="10">
-        <item h="1" x="2"/>
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item m="1" x="7"/>
-        <item m="1" x="8"/>
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="5"/>
-        <item m="1" x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="16"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="6"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="4">
-    <pageField fld="7" hier="-1"/>
-    <pageField fld="1" hier="-1"/>
-    <pageField fld="18" hier="-1"/>
-    <pageField fld="10" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Total amount in $" fld="12" baseField="16" baseItem="4"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="36">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="5">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="16" count="5">
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <chartFormats count="4">
-    <chartFormat chart="2" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:Y501" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:Y501" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="18">
       <filters>
-        <filter val="Graduate"/>
+        <filter val="PhD"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -32904,7 +32904,7 @@
       <c r="X2" s="53"/>
       <c r="Y2" s="53"/>
     </row>
-    <row r="3" spans="1:25" hidden="1">
+    <row r="3" spans="1:25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -32968,7 +32968,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" hidden="1">
+    <row r="4" spans="1:25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -33032,7 +33032,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" hidden="1">
+    <row r="5" spans="1:25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -33096,7 +33096,7 @@
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
     </row>
-    <row r="6" spans="1:25" hidden="1">
+    <row r="6" spans="1:25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -33160,7 +33160,7 @@
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
     </row>
-    <row r="7" spans="1:25" hidden="1">
+    <row r="7" spans="1:25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -33224,7 +33224,7 @@
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
     </row>
-    <row r="8" spans="1:25" hidden="1">
+    <row r="8" spans="1:25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -33288,7 +33288,7 @@
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
     </row>
-    <row r="9" spans="1:25" hidden="1">
+    <row r="9" spans="1:25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -33352,7 +33352,7 @@
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
     </row>
-    <row r="10" spans="1:25" hidden="1">
+    <row r="10" spans="1:25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -33416,7 +33416,7 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
     </row>
-    <row r="11" spans="1:25" hidden="1">
+    <row r="11" spans="1:25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -33480,7 +33480,7 @@
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
     </row>
-    <row r="12" spans="1:25" hidden="1">
+    <row r="12" spans="1:25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -33542,7 +33542,7 @@
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
     </row>
-    <row r="13" spans="1:25" hidden="1">
+    <row r="13" spans="1:25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -33606,7 +33606,7 @@
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
     </row>
-    <row r="14" spans="1:25" hidden="1">
+    <row r="14" spans="1:25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -33670,7 +33670,7 @@
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
     </row>
-    <row r="15" spans="1:25" hidden="1">
+    <row r="15" spans="1:25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -33734,7 +33734,7 @@
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
     </row>
-    <row r="16" spans="1:25" hidden="1">
+    <row r="16" spans="1:25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -33796,7 +33796,7 @@
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
     </row>
-    <row r="17" spans="1:25" hidden="1">
+    <row r="17" spans="1:25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -33858,7 +33858,7 @@
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
     </row>
-    <row r="18" spans="1:25" hidden="1">
+    <row r="18" spans="1:25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -33920,7 +33920,7 @@
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
     </row>
-    <row r="19" spans="1:25" hidden="1">
+    <row r="19" spans="1:25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -33982,7 +33982,7 @@
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
     </row>
-    <row r="20" spans="1:25" hidden="1">
+    <row r="20" spans="1:25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -34044,7 +34044,7 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
     </row>
-    <row r="21" spans="1:25" hidden="1">
+    <row r="21" spans="1:25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -34106,7 +34106,7 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
     </row>
-    <row r="22" spans="1:25" hidden="1">
+    <row r="22" spans="1:25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -34168,7 +34168,7 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
     </row>
-    <row r="23" spans="1:25" hidden="1">
+    <row r="23" spans="1:25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -34232,7 +34232,7 @@
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
     </row>
-    <row r="24" spans="1:25" hidden="1">
+    <row r="24" spans="1:25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -34296,7 +34296,7 @@
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
     </row>
-    <row r="25" spans="1:25" hidden="1">
+    <row r="25" spans="1:25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -34360,7 +34360,7 @@
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
     </row>
-    <row r="26" spans="1:25" hidden="1">
+    <row r="26" spans="1:25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -34424,7 +34424,7 @@
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
     </row>
-    <row r="27" spans="1:25" hidden="1">
+    <row r="27" spans="1:25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -34488,7 +34488,7 @@
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
     </row>
-    <row r="28" spans="1:25" hidden="1">
+    <row r="28" spans="1:25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -34552,7 +34552,7 @@
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
     </row>
-    <row r="29" spans="1:25" hidden="1">
+    <row r="29" spans="1:25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -34616,7 +34616,7 @@
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
     </row>
-    <row r="30" spans="1:25" hidden="1">
+    <row r="30" spans="1:25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -34678,7 +34678,7 @@
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
     </row>
-    <row r="31" spans="1:25" hidden="1">
+    <row r="31" spans="1:25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -34738,7 +34738,7 @@
       <c r="X31" s="4"/>
       <c r="Y31" s="4"/>
     </row>
-    <row r="32" spans="1:25" hidden="1">
+    <row r="32" spans="1:25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -34802,7 +34802,7 @@
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
     </row>
-    <row r="33" spans="1:25" hidden="1">
+    <row r="33" spans="1:25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -34864,7 +34864,7 @@
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
     </row>
-    <row r="34" spans="1:25" hidden="1">
+    <row r="34" spans="1:25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -34924,7 +34924,7 @@
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
     </row>
-    <row r="35" spans="1:25" hidden="1">
+    <row r="35" spans="1:25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -34986,7 +34986,7 @@
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
     </row>
-    <row r="36" spans="1:25" hidden="1">
+    <row r="36" spans="1:25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -35048,7 +35048,7 @@
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
     </row>
-    <row r="37" spans="1:25" hidden="1">
+    <row r="37" spans="1:25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -35108,7 +35108,7 @@
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
     </row>
-    <row r="38" spans="1:25" hidden="1">
+    <row r="38" spans="1:25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -35168,7 +35168,7 @@
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
     </row>
-    <row r="39" spans="1:25" hidden="1">
+    <row r="39" spans="1:25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -35230,7 +35230,7 @@
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
     </row>
-    <row r="40" spans="1:25" hidden="1">
+    <row r="40" spans="1:25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -35294,7 +35294,7 @@
       <c r="X40" s="4"/>
       <c r="Y40" s="4"/>
     </row>
-    <row r="41" spans="1:25" hidden="1">
+    <row r="41" spans="1:25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -35358,7 +35358,7 @@
       <c r="X41" s="4"/>
       <c r="Y41" s="4"/>
     </row>
-    <row r="42" spans="1:25" hidden="1">
+    <row r="42" spans="1:25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -35420,7 +35420,7 @@
       <c r="X42" s="4"/>
       <c r="Y42" s="4"/>
     </row>
-    <row r="43" spans="1:25" hidden="1">
+    <row r="43" spans="1:25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -35484,7 +35484,7 @@
       <c r="X43" s="4"/>
       <c r="Y43" s="4"/>
     </row>
-    <row r="44" spans="1:25" hidden="1">
+    <row r="44" spans="1:25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -35546,7 +35546,7 @@
       <c r="X44" s="4"/>
       <c r="Y44" s="4"/>
     </row>
-    <row r="45" spans="1:25" hidden="1">
+    <row r="45" spans="1:25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -35610,7 +35610,7 @@
       <c r="X45" s="4"/>
       <c r="Y45" s="4"/>
     </row>
-    <row r="46" spans="1:25" hidden="1">
+    <row r="46" spans="1:25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -35668,7 +35668,7 @@
       <c r="X46" s="4"/>
       <c r="Y46" s="4"/>
     </row>
-    <row r="47" spans="1:25" hidden="1">
+    <row r="47" spans="1:25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -35732,7 +35732,7 @@
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
     </row>
-    <row r="48" spans="1:25" hidden="1">
+    <row r="48" spans="1:25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -35796,7 +35796,7 @@
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
     </row>
-    <row r="49" spans="1:25" hidden="1">
+    <row r="49" spans="1:25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -35860,7 +35860,7 @@
       <c r="X49" s="4"/>
       <c r="Y49" s="4"/>
     </row>
-    <row r="50" spans="1:25" hidden="1">
+    <row r="50" spans="1:25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -35924,7 +35924,7 @@
       <c r="X50" s="4"/>
       <c r="Y50" s="4"/>
     </row>
-    <row r="51" spans="1:25" hidden="1">
+    <row r="51" spans="1:25">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -35986,7 +35986,7 @@
       <c r="X51" s="4"/>
       <c r="Y51" s="4"/>
     </row>
-    <row r="52" spans="1:25" hidden="1">
+    <row r="52" spans="1:25">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -36048,7 +36048,7 @@
       <c r="X52" s="4"/>
       <c r="Y52" s="4"/>
     </row>
-    <row r="53" spans="1:25" hidden="1">
+    <row r="53" spans="1:25">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -36110,7 +36110,7 @@
       <c r="X53" s="4"/>
       <c r="Y53" s="4"/>
     </row>
-    <row r="54" spans="1:25" hidden="1">
+    <row r="54" spans="1:25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -36170,7 +36170,7 @@
       <c r="X54" s="4"/>
       <c r="Y54" s="4"/>
     </row>
-    <row r="55" spans="1:25" hidden="1">
+    <row r="55" spans="1:25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -36234,7 +36234,7 @@
       <c r="X55" s="4"/>
       <c r="Y55" s="4"/>
     </row>
-    <row r="56" spans="1:25" hidden="1">
+    <row r="56" spans="1:25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -36296,7 +36296,7 @@
       <c r="X56" s="4"/>
       <c r="Y56" s="4"/>
     </row>
-    <row r="57" spans="1:25" hidden="1">
+    <row r="57" spans="1:25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -36358,7 +36358,7 @@
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
     </row>
-    <row r="58" spans="1:25" hidden="1">
+    <row r="58" spans="1:25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -36418,7 +36418,7 @@
       <c r="X58" s="4"/>
       <c r="Y58" s="4"/>
     </row>
-    <row r="59" spans="1:25" hidden="1">
+    <row r="59" spans="1:25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -36482,7 +36482,7 @@
       <c r="X59" s="4"/>
       <c r="Y59" s="4"/>
     </row>
-    <row r="60" spans="1:25" hidden="1">
+    <row r="60" spans="1:25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -36546,7 +36546,7 @@
       <c r="X60" s="4"/>
       <c r="Y60" s="4"/>
     </row>
-    <row r="61" spans="1:25" hidden="1">
+    <row r="61" spans="1:25">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -36608,7 +36608,7 @@
       <c r="X61" s="4"/>
       <c r="Y61" s="4"/>
     </row>
-    <row r="62" spans="1:25" hidden="1">
+    <row r="62" spans="1:25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -36672,7 +36672,7 @@
       <c r="X62" s="4"/>
       <c r="Y62" s="4"/>
     </row>
-    <row r="63" spans="1:25" hidden="1">
+    <row r="63" spans="1:25">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -36736,7 +36736,7 @@
       <c r="X63" s="4"/>
       <c r="Y63" s="4"/>
     </row>
-    <row r="64" spans="1:25" hidden="1">
+    <row r="64" spans="1:25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -36798,7 +36798,7 @@
       <c r="X64" s="4"/>
       <c r="Y64" s="4"/>
     </row>
-    <row r="65" spans="1:25" hidden="1">
+    <row r="65" spans="1:25">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -36858,7 +36858,7 @@
       <c r="X65" s="4"/>
       <c r="Y65" s="4"/>
     </row>
-    <row r="66" spans="1:25" hidden="1">
+    <row r="66" spans="1:25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -36920,7 +36920,7 @@
       <c r="X66" s="4"/>
       <c r="Y66" s="4"/>
     </row>
-    <row r="67" spans="1:25" hidden="1">
+    <row r="67" spans="1:25">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -36982,7 +36982,7 @@
       <c r="X67" s="4"/>
       <c r="Y67" s="4"/>
     </row>
-    <row r="68" spans="1:25" hidden="1">
+    <row r="68" spans="1:25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -37046,7 +37046,7 @@
       <c r="X68" s="4"/>
       <c r="Y68" s="4"/>
     </row>
-    <row r="69" spans="1:25" hidden="1">
+    <row r="69" spans="1:25">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -37108,7 +37108,7 @@
       <c r="X69" s="4"/>
       <c r="Y69" s="4"/>
     </row>
-    <row r="70" spans="1:25" hidden="1">
+    <row r="70" spans="1:25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -37170,7 +37170,7 @@
       <c r="X70" s="4"/>
       <c r="Y70" s="4"/>
     </row>
-    <row r="71" spans="1:25" hidden="1">
+    <row r="71" spans="1:25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -37232,7 +37232,7 @@
       <c r="X71" s="4"/>
       <c r="Y71" s="4"/>
     </row>
-    <row r="72" spans="1:25" hidden="1">
+    <row r="72" spans="1:25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -37292,7 +37292,7 @@
       <c r="X72" s="4"/>
       <c r="Y72" s="4"/>
     </row>
-    <row r="73" spans="1:25" hidden="1">
+    <row r="73" spans="1:25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -37354,7 +37354,7 @@
       <c r="X73" s="4"/>
       <c r="Y73" s="4"/>
     </row>
-    <row r="74" spans="1:25" hidden="1">
+    <row r="74" spans="1:25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -37418,7 +37418,7 @@
       <c r="X74" s="4"/>
       <c r="Y74" s="4"/>
     </row>
-    <row r="75" spans="1:25" hidden="1">
+    <row r="75" spans="1:25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -37480,7 +37480,7 @@
       <c r="X75" s="4"/>
       <c r="Y75" s="4"/>
     </row>
-    <row r="76" spans="1:25" hidden="1">
+    <row r="76" spans="1:25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -37544,7 +37544,7 @@
       <c r="X76" s="4"/>
       <c r="Y76" s="4"/>
     </row>
-    <row r="77" spans="1:25" hidden="1">
+    <row r="77" spans="1:25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -37608,7 +37608,7 @@
       <c r="X77" s="4"/>
       <c r="Y77" s="4"/>
     </row>
-    <row r="78" spans="1:25" hidden="1">
+    <row r="78" spans="1:25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -37672,7 +37672,7 @@
       <c r="X78" s="4"/>
       <c r="Y78" s="4"/>
     </row>
-    <row r="79" spans="1:25" hidden="1">
+    <row r="79" spans="1:25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -37736,7 +37736,7 @@
       <c r="X79" s="4"/>
       <c r="Y79" s="4"/>
     </row>
-    <row r="80" spans="1:25" hidden="1">
+    <row r="80" spans="1:25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -37796,7 +37796,7 @@
       <c r="X80" s="4"/>
       <c r="Y80" s="4"/>
     </row>
-    <row r="81" spans="1:25" hidden="1">
+    <row r="81" spans="1:25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -37860,7 +37860,7 @@
       <c r="X81" s="4"/>
       <c r="Y81" s="4"/>
     </row>
-    <row r="82" spans="1:25" hidden="1">
+    <row r="82" spans="1:25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -37922,7 +37922,7 @@
       <c r="X82" s="4"/>
       <c r="Y82" s="4"/>
     </row>
-    <row r="83" spans="1:25" hidden="1">
+    <row r="83" spans="1:25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -37986,7 +37986,7 @@
       <c r="X83" s="4"/>
       <c r="Y83" s="4"/>
     </row>
-    <row r="84" spans="1:25" hidden="1">
+    <row r="84" spans="1:25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -38050,7 +38050,7 @@
       <c r="X84" s="4"/>
       <c r="Y84" s="4"/>
     </row>
-    <row r="85" spans="1:25" hidden="1">
+    <row r="85" spans="1:25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -38112,7 +38112,7 @@
       <c r="X85" s="4"/>
       <c r="Y85" s="4"/>
     </row>
-    <row r="86" spans="1:25" hidden="1">
+    <row r="86" spans="1:25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -38176,7 +38176,7 @@
       <c r="X86" s="4"/>
       <c r="Y86" s="4"/>
     </row>
-    <row r="87" spans="1:25" hidden="1">
+    <row r="87" spans="1:25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -38238,7 +38238,7 @@
       <c r="X87" s="4"/>
       <c r="Y87" s="4"/>
     </row>
-    <row r="88" spans="1:25" hidden="1">
+    <row r="88" spans="1:25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -38302,7 +38302,7 @@
       <c r="X88" s="4"/>
       <c r="Y88" s="4"/>
     </row>
-    <row r="89" spans="1:25" hidden="1">
+    <row r="89" spans="1:25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -38364,7 +38364,7 @@
       <c r="X89" s="4"/>
       <c r="Y89" s="4"/>
     </row>
-    <row r="90" spans="1:25" hidden="1">
+    <row r="90" spans="1:25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -38426,7 +38426,7 @@
       <c r="X90" s="4"/>
       <c r="Y90" s="4"/>
     </row>
-    <row r="91" spans="1:25" hidden="1">
+    <row r="91" spans="1:25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -38488,7 +38488,7 @@
       <c r="X91" s="4"/>
       <c r="Y91" s="4"/>
     </row>
-    <row r="92" spans="1:25" hidden="1">
+    <row r="92" spans="1:25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -38552,7 +38552,7 @@
       <c r="X92" s="4"/>
       <c r="Y92" s="4"/>
     </row>
-    <row r="93" spans="1:25" hidden="1">
+    <row r="93" spans="1:25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -38616,7 +38616,7 @@
       <c r="X93" s="4"/>
       <c r="Y93" s="4"/>
     </row>
-    <row r="94" spans="1:25" hidden="1">
+    <row r="94" spans="1:25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -38680,7 +38680,7 @@
       <c r="X94" s="4"/>
       <c r="Y94" s="4"/>
     </row>
-    <row r="95" spans="1:25" hidden="1">
+    <row r="95" spans="1:25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -38744,7 +38744,7 @@
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
     </row>
-    <row r="96" spans="1:25" hidden="1">
+    <row r="96" spans="1:25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -38808,7 +38808,7 @@
       <c r="X96" s="4"/>
       <c r="Y96" s="4"/>
     </row>
-    <row r="97" spans="1:25" hidden="1">
+    <row r="97" spans="1:25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -38872,7 +38872,7 @@
       <c r="X97" s="4"/>
       <c r="Y97" s="4"/>
     </row>
-    <row r="98" spans="1:25" hidden="1">
+    <row r="98" spans="1:25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -38936,7 +38936,7 @@
       <c r="X98" s="4"/>
       <c r="Y98" s="4"/>
     </row>
-    <row r="99" spans="1:25" hidden="1">
+    <row r="99" spans="1:25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -39000,7 +39000,7 @@
       <c r="X99" s="4"/>
       <c r="Y99" s="4"/>
     </row>
-    <row r="100" spans="1:25" hidden="1">
+    <row r="100" spans="1:25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -39064,7 +39064,7 @@
       <c r="X100" s="4"/>
       <c r="Y100" s="4"/>
     </row>
-    <row r="101" spans="1:25" hidden="1">
+    <row r="101" spans="1:25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -39128,7 +39128,7 @@
       <c r="X101" s="4"/>
       <c r="Y101" s="4"/>
     </row>
-    <row r="102" spans="1:25" hidden="1">
+    <row r="102" spans="1:25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -39192,7 +39192,7 @@
       <c r="X102" s="4"/>
       <c r="Y102" s="4"/>
     </row>
-    <row r="103" spans="1:25" hidden="1">
+    <row r="103" spans="1:25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -39256,7 +39256,7 @@
       <c r="X103" s="4"/>
       <c r="Y103" s="4"/>
     </row>
-    <row r="104" spans="1:25" hidden="1">
+    <row r="104" spans="1:25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -39318,7 +39318,7 @@
       <c r="X104" s="4"/>
       <c r="Y104" s="4"/>
     </row>
-    <row r="105" spans="1:25" hidden="1">
+    <row r="105" spans="1:25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -39382,7 +39382,7 @@
       <c r="X105" s="4"/>
       <c r="Y105" s="4"/>
     </row>
-    <row r="106" spans="1:25" hidden="1">
+    <row r="106" spans="1:25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -39444,7 +39444,7 @@
       <c r="X106" s="4"/>
       <c r="Y106" s="4"/>
     </row>
-    <row r="107" spans="1:25" hidden="1">
+    <row r="107" spans="1:25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -39506,7 +39506,7 @@
       <c r="X107" s="4"/>
       <c r="Y107" s="4"/>
     </row>
-    <row r="108" spans="1:25" hidden="1">
+    <row r="108" spans="1:25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -39570,7 +39570,7 @@
       <c r="X108" s="4"/>
       <c r="Y108" s="4"/>
     </row>
-    <row r="109" spans="1:25" hidden="1">
+    <row r="109" spans="1:25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -39630,7 +39630,7 @@
       <c r="X109" s="4"/>
       <c r="Y109" s="4"/>
     </row>
-    <row r="110" spans="1:25" hidden="1">
+    <row r="110" spans="1:25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -39694,7 +39694,7 @@
       <c r="X110" s="4"/>
       <c r="Y110" s="4"/>
     </row>
-    <row r="111" spans="1:25" hidden="1">
+    <row r="111" spans="1:25">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -39758,7 +39758,7 @@
       <c r="X111" s="4"/>
       <c r="Y111" s="4"/>
     </row>
-    <row r="112" spans="1:25" hidden="1">
+    <row r="112" spans="1:25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -39818,7 +39818,7 @@
       <c r="X112" s="4"/>
       <c r="Y112" s="4"/>
     </row>
-    <row r="113" spans="1:25" hidden="1">
+    <row r="113" spans="1:25">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -39882,7 +39882,7 @@
       <c r="X113" s="4"/>
       <c r="Y113" s="4"/>
     </row>
-    <row r="114" spans="1:25" hidden="1">
+    <row r="114" spans="1:25">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -39946,7 +39946,7 @@
       <c r="X114" s="4"/>
       <c r="Y114" s="4"/>
     </row>
-    <row r="115" spans="1:25" hidden="1">
+    <row r="115" spans="1:25">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -40008,7 +40008,7 @@
       <c r="X115" s="4"/>
       <c r="Y115" s="4"/>
     </row>
-    <row r="116" spans="1:25" hidden="1">
+    <row r="116" spans="1:25">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -40072,7 +40072,7 @@
       <c r="X116" s="4"/>
       <c r="Y116" s="4"/>
     </row>
-    <row r="117" spans="1:25" hidden="1">
+    <row r="117" spans="1:25">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -40136,7 +40136,7 @@
       <c r="X117" s="4"/>
       <c r="Y117" s="4"/>
     </row>
-    <row r="118" spans="1:25" hidden="1">
+    <row r="118" spans="1:25">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -40200,7 +40200,7 @@
       <c r="X118" s="4"/>
       <c r="Y118" s="4"/>
     </row>
-    <row r="119" spans="1:25" hidden="1">
+    <row r="119" spans="1:25">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -40264,7 +40264,7 @@
       <c r="X119" s="4"/>
       <c r="Y119" s="4"/>
     </row>
-    <row r="120" spans="1:25" hidden="1">
+    <row r="120" spans="1:25">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -40328,7 +40328,7 @@
       <c r="X120" s="4"/>
       <c r="Y120" s="4"/>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" hidden="1">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -40392,7 +40392,7 @@
       <c r="X121" s="4"/>
       <c r="Y121" s="4"/>
     </row>
-    <row r="122" spans="1:25" hidden="1">
+    <row r="122" spans="1:25">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -40456,7 +40456,7 @@
       <c r="X122" s="4"/>
       <c r="Y122" s="4"/>
     </row>
-    <row r="123" spans="1:25" hidden="1">
+    <row r="123" spans="1:25">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -40520,7 +40520,7 @@
       <c r="X123" s="4"/>
       <c r="Y123" s="4"/>
     </row>
-    <row r="124" spans="1:25" hidden="1">
+    <row r="124" spans="1:25">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -40582,7 +40582,7 @@
       <c r="X124" s="4"/>
       <c r="Y124" s="4"/>
     </row>
-    <row r="125" spans="1:25" hidden="1">
+    <row r="125" spans="1:25">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -40644,7 +40644,7 @@
       <c r="X125" s="4"/>
       <c r="Y125" s="4"/>
     </row>
-    <row r="126" spans="1:25" hidden="1">
+    <row r="126" spans="1:25">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -40708,7 +40708,7 @@
       <c r="X126" s="4"/>
       <c r="Y126" s="4"/>
     </row>
-    <row r="127" spans="1:25" hidden="1">
+    <row r="127" spans="1:25">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -40772,7 +40772,7 @@
       <c r="X127" s="4"/>
       <c r="Y127" s="4"/>
     </row>
-    <row r="128" spans="1:25" hidden="1">
+    <row r="128" spans="1:25">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -40836,7 +40836,7 @@
       <c r="X128" s="4"/>
       <c r="Y128" s="4"/>
     </row>
-    <row r="129" spans="1:25" hidden="1">
+    <row r="129" spans="1:25">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -40900,7 +40900,7 @@
       <c r="X129" s="4"/>
       <c r="Y129" s="4"/>
     </row>
-    <row r="130" spans="1:25" hidden="1">
+    <row r="130" spans="1:25">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -40964,7 +40964,7 @@
       <c r="X130" s="4"/>
       <c r="Y130" s="4"/>
     </row>
-    <row r="131" spans="1:25" hidden="1">
+    <row r="131" spans="1:25">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -41024,7 +41024,7 @@
       <c r="X131" s="4"/>
       <c r="Y131" s="4"/>
     </row>
-    <row r="132" spans="1:25" hidden="1">
+    <row r="132" spans="1:25">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -41086,7 +41086,7 @@
       <c r="X132" s="4"/>
       <c r="Y132" s="4"/>
     </row>
-    <row r="133" spans="1:25" hidden="1">
+    <row r="133" spans="1:25">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -41150,7 +41150,7 @@
       <c r="X133" s="4"/>
       <c r="Y133" s="4"/>
     </row>
-    <row r="134" spans="1:25" hidden="1">
+    <row r="134" spans="1:25">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -41210,7 +41210,7 @@
       <c r="X134" s="4"/>
       <c r="Y134" s="4"/>
     </row>
-    <row r="135" spans="1:25" hidden="1">
+    <row r="135" spans="1:25">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -41272,7 +41272,7 @@
       <c r="X135" s="4"/>
       <c r="Y135" s="4"/>
     </row>
-    <row r="136" spans="1:25" hidden="1">
+    <row r="136" spans="1:25">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -41336,7 +41336,7 @@
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
     </row>
-    <row r="137" spans="1:25" hidden="1">
+    <row r="137" spans="1:25">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -41398,7 +41398,7 @@
       <c r="X137" s="4"/>
       <c r="Y137" s="4"/>
     </row>
-    <row r="138" spans="1:25" hidden="1">
+    <row r="138" spans="1:25">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -41462,7 +41462,7 @@
       <c r="X138" s="4"/>
       <c r="Y138" s="4"/>
     </row>
-    <row r="139" spans="1:25" hidden="1">
+    <row r="139" spans="1:25">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -41526,7 +41526,7 @@
       <c r="X139" s="4"/>
       <c r="Y139" s="4"/>
     </row>
-    <row r="140" spans="1:25" hidden="1">
+    <row r="140" spans="1:25">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -41590,7 +41590,7 @@
       <c r="X140" s="4"/>
       <c r="Y140" s="4"/>
     </row>
-    <row r="141" spans="1:25" hidden="1">
+    <row r="141" spans="1:25">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -41654,7 +41654,7 @@
       <c r="X141" s="4"/>
       <c r="Y141" s="4"/>
     </row>
-    <row r="142" spans="1:25" hidden="1">
+    <row r="142" spans="1:25">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -41718,7 +41718,7 @@
       <c r="X142" s="4"/>
       <c r="Y142" s="4"/>
     </row>
-    <row r="143" spans="1:25" hidden="1">
+    <row r="143" spans="1:25">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -41778,7 +41778,7 @@
       <c r="X143" s="4"/>
       <c r="Y143" s="4"/>
     </row>
-    <row r="144" spans="1:25" hidden="1">
+    <row r="144" spans="1:25">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -41840,7 +41840,7 @@
       <c r="X144" s="4"/>
       <c r="Y144" s="4"/>
     </row>
-    <row r="145" spans="1:25" hidden="1">
+    <row r="145" spans="1:25">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -41902,7 +41902,7 @@
       <c r="X145" s="4"/>
       <c r="Y145" s="4"/>
     </row>
-    <row r="146" spans="1:25" hidden="1">
+    <row r="146" spans="1:25">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -41962,7 +41962,7 @@
       <c r="X146" s="4"/>
       <c r="Y146" s="4"/>
     </row>
-    <row r="147" spans="1:25" hidden="1">
+    <row r="147" spans="1:25">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -42026,7 +42026,7 @@
       <c r="X147" s="4"/>
       <c r="Y147" s="4"/>
     </row>
-    <row r="148" spans="1:25" hidden="1">
+    <row r="148" spans="1:25">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -42090,7 +42090,7 @@
       <c r="X148" s="4"/>
       <c r="Y148" s="4"/>
     </row>
-    <row r="149" spans="1:25" hidden="1">
+    <row r="149" spans="1:25">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -42154,7 +42154,7 @@
       <c r="X149" s="4"/>
       <c r="Y149" s="4"/>
     </row>
-    <row r="150" spans="1:25" hidden="1">
+    <row r="150" spans="1:25">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -42218,7 +42218,7 @@
       <c r="X150" s="4"/>
       <c r="Y150" s="4"/>
     </row>
-    <row r="151" spans="1:25" hidden="1">
+    <row r="151" spans="1:25">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -42282,7 +42282,7 @@
       <c r="X151" s="4"/>
       <c r="Y151" s="4"/>
     </row>
-    <row r="152" spans="1:25" hidden="1">
+    <row r="152" spans="1:25">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -42346,7 +42346,7 @@
       <c r="X152" s="4"/>
       <c r="Y152" s="4"/>
     </row>
-    <row r="153" spans="1:25" hidden="1">
+    <row r="153" spans="1:25">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -42408,7 +42408,7 @@
       <c r="X153" s="4"/>
       <c r="Y153" s="4"/>
     </row>
-    <row r="154" spans="1:25" hidden="1">
+    <row r="154" spans="1:25">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -42472,7 +42472,7 @@
       <c r="X154" s="4"/>
       <c r="Y154" s="4"/>
     </row>
-    <row r="155" spans="1:25" hidden="1">
+    <row r="155" spans="1:25">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -42534,7 +42534,7 @@
       <c r="X155" s="4"/>
       <c r="Y155" s="4"/>
     </row>
-    <row r="156" spans="1:25" hidden="1">
+    <row r="156" spans="1:25">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -42598,7 +42598,7 @@
       <c r="X156" s="4"/>
       <c r="Y156" s="4"/>
     </row>
-    <row r="157" spans="1:25" hidden="1">
+    <row r="157" spans="1:25">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -42662,7 +42662,7 @@
       <c r="X157" s="4"/>
       <c r="Y157" s="4"/>
     </row>
-    <row r="158" spans="1:25" hidden="1">
+    <row r="158" spans="1:25">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -42720,7 +42720,7 @@
       <c r="X158" s="4"/>
       <c r="Y158" s="4"/>
     </row>
-    <row r="159" spans="1:25" hidden="1">
+    <row r="159" spans="1:25">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -42782,7 +42782,7 @@
       <c r="X159" s="4"/>
       <c r="Y159" s="4"/>
     </row>
-    <row r="160" spans="1:25" hidden="1">
+    <row r="160" spans="1:25">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -42846,7 +42846,7 @@
       <c r="X160" s="4"/>
       <c r="Y160" s="4"/>
     </row>
-    <row r="161" spans="1:25" hidden="1">
+    <row r="161" spans="1:25">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -42908,7 +42908,7 @@
       <c r="X161" s="4"/>
       <c r="Y161" s="4"/>
     </row>
-    <row r="162" spans="1:25" hidden="1">
+    <row r="162" spans="1:25">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -42972,7 +42972,7 @@
       <c r="X162" s="4"/>
       <c r="Y162" s="4"/>
     </row>
-    <row r="163" spans="1:25" hidden="1">
+    <row r="163" spans="1:25">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -43036,7 +43036,7 @@
       <c r="X163" s="4"/>
       <c r="Y163" s="4"/>
     </row>
-    <row r="164" spans="1:25" hidden="1">
+    <row r="164" spans="1:25">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -43100,7 +43100,7 @@
       <c r="X164" s="4"/>
       <c r="Y164" s="4"/>
     </row>
-    <row r="165" spans="1:25" hidden="1">
+    <row r="165" spans="1:25">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -43162,7 +43162,7 @@
       <c r="X165" s="4"/>
       <c r="Y165" s="4"/>
     </row>
-    <row r="166" spans="1:25" hidden="1">
+    <row r="166" spans="1:25">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -43224,7 +43224,7 @@
       <c r="X166" s="4"/>
       <c r="Y166" s="4"/>
     </row>
-    <row r="167" spans="1:25" hidden="1">
+    <row r="167" spans="1:25">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -43288,7 +43288,7 @@
       <c r="X167" s="4"/>
       <c r="Y167" s="4"/>
     </row>
-    <row r="168" spans="1:25">
+    <row r="168" spans="1:25" hidden="1">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -43350,7 +43350,7 @@
       <c r="X168" s="4"/>
       <c r="Y168" s="4"/>
     </row>
-    <row r="169" spans="1:25">
+    <row r="169" spans="1:25" hidden="1">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -43412,7 +43412,7 @@
       <c r="X169" s="4"/>
       <c r="Y169" s="4"/>
     </row>
-    <row r="170" spans="1:25">
+    <row r="170" spans="1:25" hidden="1">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -43474,7 +43474,7 @@
       <c r="X170" s="4"/>
       <c r="Y170" s="4"/>
     </row>
-    <row r="171" spans="1:25">
+    <row r="171" spans="1:25" hidden="1">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -43534,7 +43534,7 @@
       <c r="X171" s="4"/>
       <c r="Y171" s="4"/>
     </row>
-    <row r="172" spans="1:25">
+    <row r="172" spans="1:25" hidden="1">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -43596,7 +43596,7 @@
       <c r="X172" s="4"/>
       <c r="Y172" s="4"/>
     </row>
-    <row r="173" spans="1:25">
+    <row r="173" spans="1:25" hidden="1">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -43658,7 +43658,7 @@
       <c r="X173" s="4"/>
       <c r="Y173" s="4"/>
     </row>
-    <row r="174" spans="1:25">
+    <row r="174" spans="1:25" hidden="1">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -43720,7 +43720,7 @@
       <c r="X174" s="4"/>
       <c r="Y174" s="4"/>
     </row>
-    <row r="175" spans="1:25">
+    <row r="175" spans="1:25" hidden="1">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -43782,7 +43782,7 @@
       <c r="X175" s="4"/>
       <c r="Y175" s="4"/>
     </row>
-    <row r="176" spans="1:25">
+    <row r="176" spans="1:25" hidden="1">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -43840,7 +43840,7 @@
       <c r="X176" s="4"/>
       <c r="Y176" s="4"/>
     </row>
-    <row r="177" spans="1:25">
+    <row r="177" spans="1:25" hidden="1">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -43902,7 +43902,7 @@
       <c r="X177" s="4"/>
       <c r="Y177" s="4"/>
     </row>
-    <row r="178" spans="1:25">
+    <row r="178" spans="1:25" hidden="1">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -43964,7 +43964,7 @@
       <c r="X178" s="4"/>
       <c r="Y178" s="4"/>
     </row>
-    <row r="179" spans="1:25">
+    <row r="179" spans="1:25" hidden="1">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -44026,7 +44026,7 @@
       <c r="X179" s="4"/>
       <c r="Y179" s="4"/>
     </row>
-    <row r="180" spans="1:25">
+    <row r="180" spans="1:25" hidden="1">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -44088,7 +44088,7 @@
       <c r="X180" s="4"/>
       <c r="Y180" s="4"/>
     </row>
-    <row r="181" spans="1:25">
+    <row r="181" spans="1:25" hidden="1">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -44150,7 +44150,7 @@
       <c r="X181" s="4"/>
       <c r="Y181" s="4"/>
     </row>
-    <row r="182" spans="1:25">
+    <row r="182" spans="1:25" hidden="1">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -44212,7 +44212,7 @@
       <c r="X182" s="4"/>
       <c r="Y182" s="4"/>
     </row>
-    <row r="183" spans="1:25">
+    <row r="183" spans="1:25" hidden="1">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -44274,7 +44274,7 @@
       <c r="X183" s="4"/>
       <c r="Y183" s="4"/>
     </row>
-    <row r="184" spans="1:25">
+    <row r="184" spans="1:25" hidden="1">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -44336,7 +44336,7 @@
       <c r="X184" s="4"/>
       <c r="Y184" s="4"/>
     </row>
-    <row r="185" spans="1:25">
+    <row r="185" spans="1:25" hidden="1">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -44398,7 +44398,7 @@
       <c r="X185" s="4"/>
       <c r="Y185" s="4"/>
     </row>
-    <row r="186" spans="1:25">
+    <row r="186" spans="1:25" hidden="1">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -44454,7 +44454,7 @@
       <c r="X186" s="4"/>
       <c r="Y186" s="4"/>
     </row>
-    <row r="187" spans="1:25">
+    <row r="187" spans="1:25" hidden="1">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -44516,7 +44516,7 @@
       <c r="X187" s="4"/>
       <c r="Y187" s="4"/>
     </row>
-    <row r="188" spans="1:25">
+    <row r="188" spans="1:25" hidden="1">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -44578,7 +44578,7 @@
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
     </row>
-    <row r="189" spans="1:25">
+    <row r="189" spans="1:25" hidden="1">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -44640,7 +44640,7 @@
       <c r="X189" s="4"/>
       <c r="Y189" s="4"/>
     </row>
-    <row r="190" spans="1:25">
+    <row r="190" spans="1:25" hidden="1">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -44702,7 +44702,7 @@
       <c r="X190" s="4"/>
       <c r="Y190" s="4"/>
     </row>
-    <row r="191" spans="1:25">
+    <row r="191" spans="1:25" hidden="1">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -44758,7 +44758,7 @@
       <c r="X191" s="4"/>
       <c r="Y191" s="4"/>
     </row>
-    <row r="192" spans="1:25">
+    <row r="192" spans="1:25" hidden="1">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -44816,7 +44816,7 @@
       <c r="X192" s="4"/>
       <c r="Y192" s="4"/>
     </row>
-    <row r="193" spans="1:25">
+    <row r="193" spans="1:25" hidden="1">
       <c r="A193" s="3">
         <v>192</v>
       </c>
@@ -44876,7 +44876,7 @@
       <c r="X193" s="4"/>
       <c r="Y193" s="4"/>
     </row>
-    <row r="194" spans="1:25">
+    <row r="194" spans="1:25" hidden="1">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -44934,7 +44934,7 @@
       <c r="X194" s="4"/>
       <c r="Y194" s="4"/>
     </row>
-    <row r="195" spans="1:25">
+    <row r="195" spans="1:25" hidden="1">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -44992,7 +44992,7 @@
       <c r="X195" s="4"/>
       <c r="Y195" s="4"/>
     </row>
-    <row r="196" spans="1:25">
+    <row r="196" spans="1:25" hidden="1">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -45050,7 +45050,7 @@
       <c r="X196" s="4"/>
       <c r="Y196" s="4"/>
     </row>
-    <row r="197" spans="1:25">
+    <row r="197" spans="1:25" hidden="1">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -45112,7 +45112,7 @@
       <c r="X197" s="4"/>
       <c r="Y197" s="4"/>
     </row>
-    <row r="198" spans="1:25">
+    <row r="198" spans="1:25" hidden="1">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -45172,7 +45172,7 @@
       <c r="X198" s="4"/>
       <c r="Y198" s="4"/>
     </row>
-    <row r="199" spans="1:25">
+    <row r="199" spans="1:25" hidden="1">
       <c r="A199" s="3">
         <v>198</v>
       </c>
@@ -45234,7 +45234,7 @@
       <c r="X199" s="4"/>
       <c r="Y199" s="4"/>
     </row>
-    <row r="200" spans="1:25">
+    <row r="200" spans="1:25" hidden="1">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -45294,7 +45294,7 @@
       <c r="X200" s="4"/>
       <c r="Y200" s="4"/>
     </row>
-    <row r="201" spans="1:25">
+    <row r="201" spans="1:25" hidden="1">
       <c r="A201" s="3">
         <v>200</v>
       </c>
@@ -45356,7 +45356,7 @@
       <c r="X201" s="4"/>
       <c r="Y201" s="4"/>
     </row>
-    <row r="202" spans="1:25">
+    <row r="202" spans="1:25" hidden="1">
       <c r="A202" s="3">
         <v>201</v>
       </c>
@@ -45414,7 +45414,7 @@
       <c r="X202" s="4"/>
       <c r="Y202" s="4"/>
     </row>
-    <row r="203" spans="1:25">
+    <row r="203" spans="1:25" hidden="1">
       <c r="A203" s="3">
         <v>202</v>
       </c>
@@ -45474,7 +45474,7 @@
       <c r="X203" s="4"/>
       <c r="Y203" s="4"/>
     </row>
-    <row r="204" spans="1:25">
+    <row r="204" spans="1:25" hidden="1">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -45534,7 +45534,7 @@
       <c r="X204" s="4"/>
       <c r="Y204" s="4"/>
     </row>
-    <row r="205" spans="1:25" hidden="1">
+    <row r="205" spans="1:25">
       <c r="A205" s="3">
         <v>204</v>
       </c>
@@ -45596,7 +45596,7 @@
       <c r="X205" s="4"/>
       <c r="Y205" s="4"/>
     </row>
-    <row r="206" spans="1:25" hidden="1">
+    <row r="206" spans="1:25">
       <c r="A206" s="3">
         <v>205</v>
       </c>
@@ -45658,7 +45658,7 @@
       <c r="X206" s="4"/>
       <c r="Y206" s="4"/>
     </row>
-    <row r="207" spans="1:25" hidden="1">
+    <row r="207" spans="1:25">
       <c r="A207" s="3">
         <v>206</v>
       </c>
@@ -45722,7 +45722,7 @@
       <c r="X207" s="4"/>
       <c r="Y207" s="4"/>
     </row>
-    <row r="208" spans="1:25">
+    <row r="208" spans="1:25" hidden="1">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -45784,7 +45784,7 @@
       <c r="X208" s="4"/>
       <c r="Y208" s="4"/>
     </row>
-    <row r="209" spans="1:25">
+    <row r="209" spans="1:25" hidden="1">
       <c r="A209" s="3">
         <v>208</v>
       </c>
@@ -45844,7 +45844,7 @@
       <c r="X209" s="4"/>
       <c r="Y209" s="4"/>
     </row>
-    <row r="210" spans="1:25">
+    <row r="210" spans="1:25" hidden="1">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -45904,7 +45904,7 @@
       <c r="X210" s="4"/>
       <c r="Y210" s="4"/>
     </row>
-    <row r="211" spans="1:25">
+    <row r="211" spans="1:25" hidden="1">
       <c r="A211" s="3">
         <v>210</v>
       </c>
@@ -45966,7 +45966,7 @@
       <c r="X211" s="4"/>
       <c r="Y211" s="4"/>
     </row>
-    <row r="212" spans="1:25">
+    <row r="212" spans="1:25" hidden="1">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -46028,7 +46028,7 @@
       <c r="X212" s="4"/>
       <c r="Y212" s="4"/>
     </row>
-    <row r="213" spans="1:25">
+    <row r="213" spans="1:25" hidden="1">
       <c r="A213" s="3">
         <v>212</v>
       </c>
@@ -46090,7 +46090,7 @@
       <c r="X213" s="4"/>
       <c r="Y213" s="4"/>
     </row>
-    <row r="214" spans="1:25">
+    <row r="214" spans="1:25" hidden="1">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -46152,7 +46152,7 @@
       <c r="X214" s="4"/>
       <c r="Y214" s="4"/>
     </row>
-    <row r="215" spans="1:25">
+    <row r="215" spans="1:25" hidden="1">
       <c r="A215" s="3">
         <v>214</v>
       </c>
@@ -46212,7 +46212,7 @@
       <c r="X215" s="4"/>
       <c r="Y215" s="4"/>
     </row>
-    <row r="216" spans="1:25">
+    <row r="216" spans="1:25" hidden="1">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -46272,7 +46272,7 @@
       <c r="X216" s="4"/>
       <c r="Y216" s="4"/>
     </row>
-    <row r="217" spans="1:25">
+    <row r="217" spans="1:25" hidden="1">
       <c r="A217" s="3">
         <v>216</v>
       </c>
@@ -46332,7 +46332,7 @@
       <c r="X217" s="4"/>
       <c r="Y217" s="4"/>
     </row>
-    <row r="218" spans="1:25">
+    <row r="218" spans="1:25" hidden="1">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -46394,7 +46394,7 @@
       <c r="X218" s="4"/>
       <c r="Y218" s="4"/>
     </row>
-    <row r="219" spans="1:25" hidden="1">
+    <row r="219" spans="1:25">
       <c r="A219" s="3">
         <v>218</v>
       </c>
@@ -46458,7 +46458,7 @@
       <c r="X219" s="4"/>
       <c r="Y219" s="4"/>
     </row>
-    <row r="220" spans="1:25" hidden="1">
+    <row r="220" spans="1:25">
       <c r="A220" s="3">
         <v>219</v>
       </c>
@@ -46522,7 +46522,7 @@
       <c r="X220" s="4"/>
       <c r="Y220" s="4"/>
     </row>
-    <row r="221" spans="1:25" hidden="1">
+    <row r="221" spans="1:25">
       <c r="A221" s="3">
         <v>220</v>
       </c>
@@ -46584,7 +46584,7 @@
       <c r="X221" s="4"/>
       <c r="Y221" s="4"/>
     </row>
-    <row r="222" spans="1:25" hidden="1">
+    <row r="222" spans="1:25">
       <c r="A222" s="3">
         <v>221</v>
       </c>
@@ -46648,7 +46648,7 @@
       <c r="X222" s="4"/>
       <c r="Y222" s="4"/>
     </row>
-    <row r="223" spans="1:25" hidden="1">
+    <row r="223" spans="1:25">
       <c r="A223" s="3">
         <v>222</v>
       </c>
@@ -46712,7 +46712,7 @@
       <c r="X223" s="4"/>
       <c r="Y223" s="4"/>
     </row>
-    <row r="224" spans="1:25" hidden="1">
+    <row r="224" spans="1:25">
       <c r="A224" s="3">
         <v>223</v>
       </c>
@@ -46772,7 +46772,7 @@
       <c r="X224" s="4"/>
       <c r="Y224" s="4"/>
     </row>
-    <row r="225" spans="1:25" hidden="1">
+    <row r="225" spans="1:25">
       <c r="A225" s="3">
         <v>224</v>
       </c>
@@ -46836,7 +46836,7 @@
       <c r="X225" s="4"/>
       <c r="Y225" s="4"/>
     </row>
-    <row r="226" spans="1:25" hidden="1">
+    <row r="226" spans="1:25">
       <c r="A226" s="3">
         <v>225</v>
       </c>
@@ -46900,7 +46900,7 @@
       <c r="X226" s="4"/>
       <c r="Y226" s="4"/>
     </row>
-    <row r="227" spans="1:25" hidden="1">
+    <row r="227" spans="1:25">
       <c r="A227" s="3">
         <v>226</v>
       </c>
@@ -46964,7 +46964,7 @@
       <c r="X227" s="4"/>
       <c r="Y227" s="4"/>
     </row>
-    <row r="228" spans="1:25" hidden="1">
+    <row r="228" spans="1:25">
       <c r="A228" s="3">
         <v>227</v>
       </c>
@@ -47028,7 +47028,7 @@
       <c r="X228" s="4"/>
       <c r="Y228" s="4"/>
     </row>
-    <row r="229" spans="1:25" hidden="1">
+    <row r="229" spans="1:25">
       <c r="A229" s="3">
         <v>228</v>
       </c>
@@ -47092,7 +47092,7 @@
       <c r="X229" s="4"/>
       <c r="Y229" s="4"/>
     </row>
-    <row r="230" spans="1:25" hidden="1">
+    <row r="230" spans="1:25">
       <c r="A230" s="3">
         <v>229</v>
       </c>
@@ -47156,7 +47156,7 @@
       <c r="X230" s="4"/>
       <c r="Y230" s="4"/>
     </row>
-    <row r="231" spans="1:25" hidden="1">
+    <row r="231" spans="1:25">
       <c r="A231" s="3">
         <v>230</v>
       </c>
@@ -47220,7 +47220,7 @@
       <c r="X231" s="4"/>
       <c r="Y231" s="4"/>
     </row>
-    <row r="232" spans="1:25" hidden="1">
+    <row r="232" spans="1:25">
       <c r="A232" s="3">
         <v>231</v>
       </c>
@@ -47284,7 +47284,7 @@
       <c r="X232" s="4"/>
       <c r="Y232" s="4"/>
     </row>
-    <row r="233" spans="1:25" hidden="1">
+    <row r="233" spans="1:25">
       <c r="A233" s="3">
         <v>232</v>
       </c>
@@ -47346,7 +47346,7 @@
       <c r="X233" s="4"/>
       <c r="Y233" s="4"/>
     </row>
-    <row r="234" spans="1:25" hidden="1">
+    <row r="234" spans="1:25">
       <c r="A234" s="3">
         <v>233</v>
       </c>
@@ -47410,7 +47410,7 @@
       <c r="X234" s="4"/>
       <c r="Y234" s="4"/>
     </row>
-    <row r="235" spans="1:25" hidden="1">
+    <row r="235" spans="1:25">
       <c r="A235" s="3">
         <v>234</v>
       </c>
@@ -47474,7 +47474,7 @@
       <c r="X235" s="4"/>
       <c r="Y235" s="4"/>
     </row>
-    <row r="236" spans="1:25" hidden="1">
+    <row r="236" spans="1:25">
       <c r="A236" s="3">
         <v>235</v>
       </c>
@@ -47538,7 +47538,7 @@
       <c r="X236" s="4"/>
       <c r="Y236" s="4"/>
     </row>
-    <row r="237" spans="1:25" hidden="1">
+    <row r="237" spans="1:25">
       <c r="A237" s="3">
         <v>236</v>
       </c>
@@ -47598,7 +47598,7 @@
       <c r="X237" s="4"/>
       <c r="Y237" s="4"/>
     </row>
-    <row r="238" spans="1:25">
+    <row r="238" spans="1:25" hidden="1">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -47660,7 +47660,7 @@
       <c r="X238" s="4"/>
       <c r="Y238" s="4"/>
     </row>
-    <row r="239" spans="1:25">
+    <row r="239" spans="1:25" hidden="1">
       <c r="A239" s="3">
         <v>238</v>
       </c>
@@ -47722,7 +47722,7 @@
       <c r="X239" s="4"/>
       <c r="Y239" s="4"/>
     </row>
-    <row r="240" spans="1:25">
+    <row r="240" spans="1:25" hidden="1">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -47784,7 +47784,7 @@
       <c r="X240" s="4"/>
       <c r="Y240" s="4"/>
     </row>
-    <row r="241" spans="1:25" hidden="1">
+    <row r="241" spans="1:25">
       <c r="A241" s="3">
         <v>240</v>
       </c>
@@ -47850,7 +47850,7 @@
       <c r="X241" s="4"/>
       <c r="Y241" s="4"/>
     </row>
-    <row r="242" spans="1:25">
+    <row r="242" spans="1:25" hidden="1">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -47914,7 +47914,7 @@
       <c r="X242" s="4"/>
       <c r="Y242" s="4"/>
     </row>
-    <row r="243" spans="1:25" hidden="1">
+    <row r="243" spans="1:25">
       <c r="A243" s="3">
         <v>242</v>
       </c>
@@ -47980,7 +47980,7 @@
       <c r="X243" s="4"/>
       <c r="Y243" s="4"/>
     </row>
-    <row r="244" spans="1:25">
+    <row r="244" spans="1:25" hidden="1">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -48042,7 +48042,7 @@
       <c r="X244" s="4"/>
       <c r="Y244" s="4"/>
     </row>
-    <row r="245" spans="1:25">
+    <row r="245" spans="1:25" hidden="1">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -48102,7 +48102,7 @@
       <c r="X245" s="4"/>
       <c r="Y245" s="4"/>
     </row>
-    <row r="246" spans="1:25">
+    <row r="246" spans="1:25" hidden="1">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -48162,7 +48162,7 @@
       <c r="X246" s="4"/>
       <c r="Y246" s="4"/>
     </row>
-    <row r="247" spans="1:25">
+    <row r="247" spans="1:25" hidden="1">
       <c r="A247" s="3">
         <v>246</v>
       </c>
@@ -48224,7 +48224,7 @@
       <c r="X247" s="4"/>
       <c r="Y247" s="4"/>
     </row>
-    <row r="248" spans="1:25" hidden="1">
+    <row r="248" spans="1:25">
       <c r="A248" s="3">
         <v>247</v>
       </c>
@@ -48288,7 +48288,7 @@
       <c r="X248" s="4"/>
       <c r="Y248" s="4"/>
     </row>
-    <row r="249" spans="1:25" hidden="1">
+    <row r="249" spans="1:25">
       <c r="A249" s="3">
         <v>248</v>
       </c>
@@ -48352,7 +48352,7 @@
       <c r="X249" s="4"/>
       <c r="Y249" s="4"/>
     </row>
-    <row r="250" spans="1:25" hidden="1">
+    <row r="250" spans="1:25">
       <c r="A250" s="3">
         <v>249</v>
       </c>
@@ -48416,7 +48416,7 @@
       <c r="X250" s="4"/>
       <c r="Y250" s="4"/>
     </row>
-    <row r="251" spans="1:25" hidden="1">
+    <row r="251" spans="1:25">
       <c r="A251" s="3">
         <v>250</v>
       </c>
@@ -48480,7 +48480,7 @@
       <c r="X251" s="4"/>
       <c r="Y251" s="4"/>
     </row>
-    <row r="252" spans="1:25" hidden="1">
+    <row r="252" spans="1:25">
       <c r="A252" s="3">
         <v>251</v>
       </c>
@@ -48544,7 +48544,7 @@
       <c r="X252" s="4"/>
       <c r="Y252" s="4"/>
     </row>
-    <row r="253" spans="1:25" hidden="1">
+    <row r="253" spans="1:25">
       <c r="A253" s="3">
         <v>252</v>
       </c>
@@ -48606,7 +48606,7 @@
       <c r="X253" s="4"/>
       <c r="Y253" s="4"/>
     </row>
-    <row r="254" spans="1:25" hidden="1">
+    <row r="254" spans="1:25">
       <c r="A254" s="3">
         <v>253</v>
       </c>
@@ -48668,7 +48668,7 @@
       <c r="X254" s="4"/>
       <c r="Y254" s="4"/>
     </row>
-    <row r="255" spans="1:25" hidden="1">
+    <row r="255" spans="1:25">
       <c r="A255" s="3">
         <v>254</v>
       </c>
@@ -48732,7 +48732,7 @@
       <c r="X255" s="4"/>
       <c r="Y255" s="4"/>
     </row>
-    <row r="256" spans="1:25" hidden="1">
+    <row r="256" spans="1:25">
       <c r="A256" s="3">
         <v>255</v>
       </c>
@@ -48796,7 +48796,7 @@
       <c r="X256" s="4"/>
       <c r="Y256" s="4"/>
     </row>
-    <row r="257" spans="1:25" hidden="1">
+    <row r="257" spans="1:25">
       <c r="A257" s="3">
         <v>256</v>
       </c>
@@ -48860,7 +48860,7 @@
       <c r="X257" s="4"/>
       <c r="Y257" s="4"/>
     </row>
-    <row r="258" spans="1:25" hidden="1">
+    <row r="258" spans="1:25">
       <c r="A258" s="3">
         <v>257</v>
       </c>
@@ -48924,7 +48924,7 @@
       <c r="X258" s="4"/>
       <c r="Y258" s="4"/>
     </row>
-    <row r="259" spans="1:25" hidden="1">
+    <row r="259" spans="1:25">
       <c r="A259" s="3">
         <v>258</v>
       </c>
@@ -48988,7 +48988,7 @@
       <c r="X259" s="4"/>
       <c r="Y259" s="4"/>
     </row>
-    <row r="260" spans="1:25" hidden="1">
+    <row r="260" spans="1:25">
       <c r="A260" s="3">
         <v>259</v>
       </c>
@@ -49052,7 +49052,7 @@
       <c r="X260" s="4"/>
       <c r="Y260" s="4"/>
     </row>
-    <row r="261" spans="1:25" hidden="1">
+    <row r="261" spans="1:25">
       <c r="A261" s="3">
         <v>260</v>
       </c>
@@ -49116,7 +49116,7 @@
       <c r="X261" s="4"/>
       <c r="Y261" s="4"/>
     </row>
-    <row r="262" spans="1:25" hidden="1">
+    <row r="262" spans="1:25">
       <c r="A262" s="3">
         <v>261</v>
       </c>
@@ -49178,7 +49178,7 @@
       <c r="X262" s="4"/>
       <c r="Y262" s="4"/>
     </row>
-    <row r="263" spans="1:25" hidden="1">
+    <row r="263" spans="1:25">
       <c r="A263" s="3">
         <v>262</v>
       </c>
@@ -49240,7 +49240,7 @@
       <c r="X263" s="4"/>
       <c r="Y263" s="4"/>
     </row>
-    <row r="264" spans="1:25" hidden="1">
+    <row r="264" spans="1:25">
       <c r="A264" s="3">
         <v>263</v>
       </c>
@@ -49304,7 +49304,7 @@
       <c r="X264" s="4"/>
       <c r="Y264" s="4"/>
     </row>
-    <row r="265" spans="1:25" hidden="1">
+    <row r="265" spans="1:25">
       <c r="A265" s="3">
         <v>264</v>
       </c>
@@ -49366,7 +49366,7 @@
       <c r="X265" s="4"/>
       <c r="Y265" s="4"/>
     </row>
-    <row r="266" spans="1:25" hidden="1">
+    <row r="266" spans="1:25">
       <c r="A266" s="3">
         <v>265</v>
       </c>
@@ -49428,7 +49428,7 @@
       <c r="X266" s="4"/>
       <c r="Y266" s="4"/>
     </row>
-    <row r="267" spans="1:25" hidden="1">
+    <row r="267" spans="1:25">
       <c r="A267" s="3">
         <v>266</v>
       </c>
@@ -49490,7 +49490,7 @@
       <c r="X267" s="4"/>
       <c r="Y267" s="4"/>
     </row>
-    <row r="268" spans="1:25" hidden="1">
+    <row r="268" spans="1:25">
       <c r="A268" s="3">
         <v>267</v>
       </c>
@@ -49550,7 +49550,7 @@
       <c r="X268" s="4"/>
       <c r="Y268" s="4"/>
     </row>
-    <row r="269" spans="1:25" hidden="1">
+    <row r="269" spans="1:25">
       <c r="A269" s="3">
         <v>268</v>
       </c>
@@ -49610,7 +49610,7 @@
       <c r="X269" s="4"/>
       <c r="Y269" s="4"/>
     </row>
-    <row r="270" spans="1:25" hidden="1">
+    <row r="270" spans="1:25">
       <c r="A270" s="3">
         <v>269</v>
       </c>
@@ -49678,7 +49678,7 @@
       <c r="X270" s="4"/>
       <c r="Y270" s="4"/>
     </row>
-    <row r="271" spans="1:25" hidden="1">
+    <row r="271" spans="1:25">
       <c r="A271" s="3">
         <v>270</v>
       </c>
@@ -49740,7 +49740,7 @@
       <c r="X271" s="4"/>
       <c r="Y271" s="4"/>
     </row>
-    <row r="272" spans="1:25">
+    <row r="272" spans="1:25" hidden="1">
       <c r="A272" s="3">
         <v>271</v>
       </c>
@@ -49800,7 +49800,7 @@
       <c r="X272" s="4"/>
       <c r="Y272" s="4"/>
     </row>
-    <row r="273" spans="1:25">
+    <row r="273" spans="1:25" hidden="1">
       <c r="A273" s="3">
         <v>272</v>
       </c>
@@ -49864,7 +49864,7 @@
       <c r="X273" s="4"/>
       <c r="Y273" s="4"/>
     </row>
-    <row r="274" spans="1:25">
+    <row r="274" spans="1:25" hidden="1">
       <c r="A274" s="3">
         <v>273</v>
       </c>
@@ -49926,7 +49926,7 @@
       <c r="X274" s="4"/>
       <c r="Y274" s="4"/>
     </row>
-    <row r="275" spans="1:25">
+    <row r="275" spans="1:25" hidden="1">
       <c r="A275" s="3">
         <v>274</v>
       </c>
@@ -49986,7 +49986,7 @@
       <c r="X275" s="4"/>
       <c r="Y275" s="4"/>
     </row>
-    <row r="276" spans="1:25">
+    <row r="276" spans="1:25" hidden="1">
       <c r="A276" s="3">
         <v>275</v>
       </c>
@@ -50048,7 +50048,7 @@
       <c r="X276" s="4"/>
       <c r="Y276" s="4"/>
     </row>
-    <row r="277" spans="1:25">
+    <row r="277" spans="1:25" hidden="1">
       <c r="A277" s="3">
         <v>276</v>
       </c>
@@ -50112,7 +50112,7 @@
       <c r="X277" s="4"/>
       <c r="Y277" s="4"/>
     </row>
-    <row r="278" spans="1:25">
+    <row r="278" spans="1:25" hidden="1">
       <c r="A278" s="3">
         <v>277</v>
       </c>
@@ -50174,7 +50174,7 @@
       <c r="X278" s="4"/>
       <c r="Y278" s="4"/>
     </row>
-    <row r="279" spans="1:25">
+    <row r="279" spans="1:25" hidden="1">
       <c r="A279" s="3">
         <v>278</v>
       </c>
@@ -50236,7 +50236,7 @@
       <c r="X279" s="4"/>
       <c r="Y279" s="4"/>
     </row>
-    <row r="280" spans="1:25">
+    <row r="280" spans="1:25" hidden="1">
       <c r="A280" s="3">
         <v>279</v>
       </c>
@@ -50300,7 +50300,7 @@
       <c r="X280" s="4"/>
       <c r="Y280" s="4"/>
     </row>
-    <row r="281" spans="1:25">
+    <row r="281" spans="1:25" hidden="1">
       <c r="A281" s="3">
         <v>280</v>
       </c>
@@ -50362,7 +50362,7 @@
       <c r="X281" s="4"/>
       <c r="Y281" s="4"/>
     </row>
-    <row r="282" spans="1:25" hidden="1">
+    <row r="282" spans="1:25">
       <c r="A282" s="3">
         <v>281</v>
       </c>
@@ -50426,7 +50426,7 @@
       <c r="X282" s="4"/>
       <c r="Y282" s="4"/>
     </row>
-    <row r="283" spans="1:25" hidden="1">
+    <row r="283" spans="1:25">
       <c r="A283" s="3">
         <v>282</v>
       </c>
@@ -50492,7 +50492,7 @@
       <c r="X283" s="4"/>
       <c r="Y283" s="4"/>
     </row>
-    <row r="284" spans="1:25" hidden="1">
+    <row r="284" spans="1:25">
       <c r="A284" s="3">
         <v>283</v>
       </c>
@@ -50558,7 +50558,7 @@
       <c r="X284" s="4"/>
       <c r="Y284" s="4"/>
     </row>
-    <row r="285" spans="1:25" hidden="1">
+    <row r="285" spans="1:25">
       <c r="A285" s="3">
         <v>284</v>
       </c>
@@ -50622,7 +50622,7 @@
       <c r="X285" s="4"/>
       <c r="Y285" s="4"/>
     </row>
-    <row r="286" spans="1:25" hidden="1">
+    <row r="286" spans="1:25">
       <c r="A286" s="3">
         <v>285</v>
       </c>
@@ -50686,7 +50686,7 @@
       <c r="X286" s="4"/>
       <c r="Y286" s="4"/>
     </row>
-    <row r="287" spans="1:25" hidden="1">
+    <row r="287" spans="1:25">
       <c r="A287" s="3">
         <v>286</v>
       </c>
@@ -50750,7 +50750,7 @@
       <c r="X287" s="4"/>
       <c r="Y287" s="4"/>
     </row>
-    <row r="288" spans="1:25" hidden="1">
+    <row r="288" spans="1:25">
       <c r="A288" s="3">
         <v>287</v>
       </c>
@@ -50814,7 +50814,7 @@
       <c r="X288" s="4"/>
       <c r="Y288" s="4"/>
     </row>
-    <row r="289" spans="1:25" hidden="1">
+    <row r="289" spans="1:25">
       <c r="A289" s="3">
         <v>288</v>
       </c>
@@ -50878,7 +50878,7 @@
       <c r="X289" s="4"/>
       <c r="Y289" s="4"/>
     </row>
-    <row r="290" spans="1:25" hidden="1">
+    <row r="290" spans="1:25">
       <c r="A290" s="3">
         <v>289</v>
       </c>
@@ -50938,7 +50938,7 @@
       <c r="X290" s="4"/>
       <c r="Y290" s="4"/>
     </row>
-    <row r="291" spans="1:25" hidden="1">
+    <row r="291" spans="1:25">
       <c r="A291" s="3">
         <v>290</v>
       </c>
@@ -51002,7 +51002,7 @@
       <c r="X291" s="4"/>
       <c r="Y291" s="4"/>
     </row>
-    <row r="292" spans="1:25" hidden="1">
+    <row r="292" spans="1:25">
       <c r="A292" s="3">
         <v>291</v>
       </c>
@@ -51066,7 +51066,7 @@
       <c r="X292" s="4"/>
       <c r="Y292" s="4"/>
     </row>
-    <row r="293" spans="1:25" hidden="1">
+    <row r="293" spans="1:25">
       <c r="A293" s="3">
         <v>292</v>
       </c>
@@ -51130,7 +51130,7 @@
       <c r="X293" s="4"/>
       <c r="Y293" s="4"/>
     </row>
-    <row r="294" spans="1:25" hidden="1">
+    <row r="294" spans="1:25">
       <c r="A294" s="3">
         <v>293</v>
       </c>
@@ -51194,7 +51194,7 @@
       <c r="X294" s="4"/>
       <c r="Y294" s="4"/>
     </row>
-    <row r="295" spans="1:25" hidden="1">
+    <row r="295" spans="1:25">
       <c r="A295" s="3">
         <v>294</v>
       </c>
@@ -51254,7 +51254,7 @@
       <c r="X295" s="4"/>
       <c r="Y295" s="4"/>
     </row>
-    <row r="296" spans="1:25">
+    <row r="296" spans="1:25" hidden="1">
       <c r="A296" s="3">
         <v>295</v>
       </c>
@@ -51318,7 +51318,7 @@
       <c r="X296" s="4"/>
       <c r="Y296" s="4"/>
     </row>
-    <row r="297" spans="1:25">
+    <row r="297" spans="1:25" hidden="1">
       <c r="A297" s="3">
         <v>296</v>
       </c>
@@ -51382,7 +51382,7 @@
       <c r="X297" s="4"/>
       <c r="Y297" s="4"/>
     </row>
-    <row r="298" spans="1:25">
+    <row r="298" spans="1:25" hidden="1">
       <c r="A298" s="3">
         <v>297</v>
       </c>
@@ -51446,7 +51446,7 @@
       <c r="X298" s="4"/>
       <c r="Y298" s="4"/>
     </row>
-    <row r="299" spans="1:25" hidden="1">
+    <row r="299" spans="1:25">
       <c r="A299" s="3">
         <v>298</v>
       </c>
@@ -51510,7 +51510,7 @@
       <c r="X299" s="4"/>
       <c r="Y299" s="4"/>
     </row>
-    <row r="300" spans="1:25">
+    <row r="300" spans="1:25" hidden="1">
       <c r="A300" s="3">
         <v>299</v>
       </c>
@@ -51570,7 +51570,7 @@
       <c r="X300" s="4"/>
       <c r="Y300" s="4"/>
     </row>
-    <row r="301" spans="1:25">
+    <row r="301" spans="1:25" hidden="1">
       <c r="A301" s="3">
         <v>300</v>
       </c>
@@ -51632,7 +51632,7 @@
       <c r="X301" s="4"/>
       <c r="Y301" s="4"/>
     </row>
-    <row r="302" spans="1:25">
+    <row r="302" spans="1:25" hidden="1">
       <c r="A302" s="3">
         <v>301</v>
       </c>
@@ -51694,7 +51694,7 @@
       <c r="X302" s="4"/>
       <c r="Y302" s="4"/>
     </row>
-    <row r="303" spans="1:25">
+    <row r="303" spans="1:25" hidden="1">
       <c r="A303" s="3">
         <v>302</v>
       </c>
@@ -51762,7 +51762,7 @@
       <c r="X303" s="4"/>
       <c r="Y303" s="4"/>
     </row>
-    <row r="304" spans="1:25">
+    <row r="304" spans="1:25" hidden="1">
       <c r="A304" s="3">
         <v>303</v>
       </c>
@@ -51826,7 +51826,7 @@
       <c r="X304" s="4"/>
       <c r="Y304" s="4"/>
     </row>
-    <row r="305" spans="1:25">
+    <row r="305" spans="1:25" hidden="1">
       <c r="A305" s="3">
         <v>304</v>
       </c>
@@ -51890,7 +51890,7 @@
       <c r="X305" s="4"/>
       <c r="Y305" s="4"/>
     </row>
-    <row r="306" spans="1:25">
+    <row r="306" spans="1:25" hidden="1">
       <c r="A306" s="3">
         <v>305</v>
       </c>
@@ -51956,7 +51956,7 @@
       <c r="X306" s="4"/>
       <c r="Y306" s="4"/>
     </row>
-    <row r="307" spans="1:25">
+    <row r="307" spans="1:25" hidden="1">
       <c r="A307" s="3">
         <v>306</v>
       </c>
@@ -52016,7 +52016,7 @@
       <c r="X307" s="4"/>
       <c r="Y307" s="4"/>
     </row>
-    <row r="308" spans="1:25" hidden="1">
+    <row r="308" spans="1:25">
       <c r="A308" s="3">
         <v>307</v>
       </c>
@@ -52086,7 +52086,7 @@
       <c r="X308" s="4"/>
       <c r="Y308" s="4"/>
     </row>
-    <row r="309" spans="1:25" hidden="1">
+    <row r="309" spans="1:25">
       <c r="A309" s="3">
         <v>308</v>
       </c>
@@ -52152,7 +52152,7 @@
       <c r="X309" s="4"/>
       <c r="Y309" s="4"/>
     </row>
-    <row r="310" spans="1:25" hidden="1">
+    <row r="310" spans="1:25">
       <c r="A310" s="3">
         <v>309</v>
       </c>
@@ -52218,7 +52218,7 @@
       <c r="X310" s="4"/>
       <c r="Y310" s="4"/>
     </row>
-    <row r="311" spans="1:25" hidden="1">
+    <row r="311" spans="1:25">
       <c r="A311" s="3">
         <v>310</v>
       </c>
@@ -52288,7 +52288,7 @@
       <c r="X311" s="4"/>
       <c r="Y311" s="4"/>
     </row>
-    <row r="312" spans="1:25" hidden="1">
+    <row r="312" spans="1:25">
       <c r="A312" s="3">
         <v>311</v>
       </c>
@@ -52356,7 +52356,7 @@
       <c r="X312" s="4"/>
       <c r="Y312" s="4"/>
     </row>
-    <row r="313" spans="1:25" hidden="1">
+    <row r="313" spans="1:25">
       <c r="A313" s="3">
         <v>312</v>
       </c>
@@ -52424,7 +52424,7 @@
       <c r="X313" s="4"/>
       <c r="Y313" s="4"/>
     </row>
-    <row r="314" spans="1:25" hidden="1">
+    <row r="314" spans="1:25">
       <c r="A314" s="3">
         <v>313</v>
       </c>
@@ -52492,7 +52492,7 @@
       <c r="X314" s="4"/>
       <c r="Y314" s="4"/>
     </row>
-    <row r="315" spans="1:25" hidden="1">
+    <row r="315" spans="1:25">
       <c r="A315" s="3">
         <v>314</v>
       </c>
@@ -52562,7 +52562,7 @@
       <c r="X315" s="4"/>
       <c r="Y315" s="4"/>
     </row>
-    <row r="316" spans="1:25" hidden="1">
+    <row r="316" spans="1:25">
       <c r="A316" s="3">
         <v>315</v>
       </c>
@@ -52632,7 +52632,7 @@
       <c r="X316" s="4"/>
       <c r="Y316" s="4"/>
     </row>
-    <row r="317" spans="1:25" hidden="1">
+    <row r="317" spans="1:25">
       <c r="A317" s="3">
         <v>316</v>
       </c>
@@ -52698,7 +52698,7 @@
       <c r="X317" s="4"/>
       <c r="Y317" s="4"/>
     </row>
-    <row r="318" spans="1:25" hidden="1">
+    <row r="318" spans="1:25">
       <c r="A318" s="3">
         <v>317</v>
       </c>
@@ -52764,7 +52764,7 @@
       <c r="X318" s="4"/>
       <c r="Y318" s="4"/>
     </row>
-    <row r="319" spans="1:25" hidden="1">
+    <row r="319" spans="1:25">
       <c r="A319" s="3">
         <v>318</v>
       </c>
@@ -52832,7 +52832,7 @@
       <c r="X319" s="4"/>
       <c r="Y319" s="4"/>
     </row>
-    <row r="320" spans="1:25" hidden="1">
+    <row r="320" spans="1:25">
       <c r="A320" s="3">
         <v>319</v>
       </c>
@@ -52898,7 +52898,7 @@
       <c r="X320" s="4"/>
       <c r="Y320" s="4"/>
     </row>
-    <row r="321" spans="1:25">
+    <row r="321" spans="1:25" hidden="1">
       <c r="A321" s="3">
         <v>320</v>
       </c>
@@ -52958,7 +52958,7 @@
       <c r="X321" s="4"/>
       <c r="Y321" s="4"/>
     </row>
-    <row r="322" spans="1:25">
+    <row r="322" spans="1:25" hidden="1">
       <c r="A322" s="3">
         <v>321</v>
       </c>
@@ -53020,7 +53020,7 @@
       <c r="X322" s="4"/>
       <c r="Y322" s="4"/>
     </row>
-    <row r="323" spans="1:25">
+    <row r="323" spans="1:25" hidden="1">
       <c r="A323" s="3">
         <v>322</v>
       </c>
@@ -53082,7 +53082,7 @@
       <c r="X323" s="4"/>
       <c r="Y323" s="4"/>
     </row>
-    <row r="324" spans="1:25">
+    <row r="324" spans="1:25" hidden="1">
       <c r="A324" s="3">
         <v>323</v>
       </c>
@@ -53146,7 +53146,7 @@
       <c r="X324" s="4"/>
       <c r="Y324" s="4"/>
     </row>
-    <row r="325" spans="1:25">
+    <row r="325" spans="1:25" hidden="1">
       <c r="A325" s="3">
         <v>324</v>
       </c>
@@ -53200,7 +53200,7 @@
       <c r="X325" s="4"/>
       <c r="Y325" s="4"/>
     </row>
-    <row r="326" spans="1:25">
+    <row r="326" spans="1:25" hidden="1">
       <c r="A326" s="3">
         <v>325</v>
       </c>
@@ -53262,7 +53262,7 @@
       <c r="X326" s="4"/>
       <c r="Y326" s="4"/>
     </row>
-    <row r="327" spans="1:25">
+    <row r="327" spans="1:25" hidden="1">
       <c r="A327" s="3">
         <v>326</v>
       </c>
@@ -53324,7 +53324,7 @@
       <c r="X327" s="4"/>
       <c r="Y327" s="4"/>
     </row>
-    <row r="328" spans="1:25" ht="14.45" hidden="1" customHeight="1">
+    <row r="328" spans="1:25" ht="14.45" customHeight="1">
       <c r="A328" s="3">
         <v>327</v>
       </c>
@@ -53380,7 +53380,7 @@
       <c r="X328" s="4"/>
       <c r="Y328" s="4"/>
     </row>
-    <row r="329" spans="1:25" ht="14.45" customHeight="1">
+    <row r="329" spans="1:25" ht="14.45" hidden="1" customHeight="1">
       <c r="A329" s="3">
         <v>328</v>
       </c>
@@ -53448,7 +53448,7 @@
       <c r="X329" s="4"/>
       <c r="Y329" s="4"/>
     </row>
-    <row r="330" spans="1:25" hidden="1">
+    <row r="330" spans="1:25">
       <c r="A330" s="3">
         <v>329</v>
       </c>
@@ -53516,7 +53516,7 @@
       <c r="X330" s="4"/>
       <c r="Y330" s="4"/>
     </row>
-    <row r="331" spans="1:25" hidden="1">
+    <row r="331" spans="1:25">
       <c r="A331" s="3">
         <v>330</v>
       </c>
@@ -53582,7 +53582,7 @@
       <c r="X331" s="4"/>
       <c r="Y331" s="4"/>
     </row>
-    <row r="332" spans="1:25" hidden="1">
+    <row r="332" spans="1:25">
       <c r="A332" s="3">
         <v>331</v>
       </c>
@@ -53648,7 +53648,7 @@
       <c r="X332" s="4"/>
       <c r="Y332" s="4"/>
     </row>
-    <row r="333" spans="1:25" hidden="1">
+    <row r="333" spans="1:25">
       <c r="A333" s="3">
         <v>332</v>
       </c>
@@ -53718,7 +53718,7 @@
       <c r="X333" s="4"/>
       <c r="Y333" s="4"/>
     </row>
-    <row r="334" spans="1:25" hidden="1">
+    <row r="334" spans="1:25">
       <c r="A334" s="3">
         <v>333</v>
       </c>
@@ -53790,7 +53790,7 @@
       <c r="X334" s="4"/>
       <c r="Y334" s="4"/>
     </row>
-    <row r="335" spans="1:25" hidden="1">
+    <row r="335" spans="1:25">
       <c r="A335" s="3">
         <v>334</v>
       </c>
@@ -53860,7 +53860,7 @@
       <c r="X335" s="4"/>
       <c r="Y335" s="4"/>
     </row>
-    <row r="336" spans="1:25" hidden="1">
+    <row r="336" spans="1:25">
       <c r="A336" s="3">
         <v>335</v>
       </c>
@@ -53930,7 +53930,7 @@
       <c r="X336" s="4"/>
       <c r="Y336" s="4"/>
     </row>
-    <row r="337" spans="1:25" hidden="1">
+    <row r="337" spans="1:25">
       <c r="A337" s="3">
         <v>336</v>
       </c>
@@ -53996,7 +53996,7 @@
       <c r="X337" s="4"/>
       <c r="Y337" s="4"/>
     </row>
-    <row r="338" spans="1:25" hidden="1">
+    <row r="338" spans="1:25">
       <c r="A338" s="3">
         <v>337</v>
       </c>
@@ -54064,7 +54064,7 @@
       <c r="X338" s="4"/>
       <c r="Y338" s="4"/>
     </row>
-    <row r="339" spans="1:25" hidden="1">
+    <row r="339" spans="1:25">
       <c r="A339" s="3">
         <v>338</v>
       </c>
@@ -54130,7 +54130,7 @@
       <c r="X339" s="4"/>
       <c r="Y339" s="4"/>
     </row>
-    <row r="340" spans="1:25" hidden="1">
+    <row r="340" spans="1:25">
       <c r="A340" s="3">
         <v>339</v>
       </c>
@@ -54198,7 +54198,7 @@
       <c r="X340" s="4"/>
       <c r="Y340" s="4"/>
     </row>
-    <row r="341" spans="1:25" hidden="1">
+    <row r="341" spans="1:25">
       <c r="A341" s="3">
         <v>340</v>
       </c>
@@ -54266,7 +54266,7 @@
       <c r="X341" s="4"/>
       <c r="Y341" s="4"/>
     </row>
-    <row r="342" spans="1:25">
+    <row r="342" spans="1:25" hidden="1">
       <c r="A342" s="3">
         <v>341</v>
       </c>
@@ -54332,7 +54332,7 @@
       <c r="X342" s="4"/>
       <c r="Y342" s="4"/>
     </row>
-    <row r="343" spans="1:25">
+    <row r="343" spans="1:25" hidden="1">
       <c r="A343" s="3">
         <v>342</v>
       </c>
@@ -54396,7 +54396,7 @@
       <c r="X343" s="4"/>
       <c r="Y343" s="4"/>
     </row>
-    <row r="344" spans="1:25">
+    <row r="344" spans="1:25" hidden="1">
       <c r="A344" s="3">
         <v>343</v>
       </c>
@@ -54462,7 +54462,7 @@
       <c r="X344" s="4"/>
       <c r="Y344" s="4"/>
     </row>
-    <row r="345" spans="1:25">
+    <row r="345" spans="1:25" hidden="1">
       <c r="A345" s="3">
         <v>344</v>
       </c>
@@ -54524,7 +54524,7 @@
       <c r="X345" s="4"/>
       <c r="Y345" s="4"/>
     </row>
-    <row r="346" spans="1:25">
+    <row r="346" spans="1:25" hidden="1">
       <c r="A346" s="3">
         <v>345</v>
       </c>
@@ -54586,7 +54586,7 @@
       <c r="X346" s="4"/>
       <c r="Y346" s="4"/>
     </row>
-    <row r="347" spans="1:25">
+    <row r="347" spans="1:25" hidden="1">
       <c r="A347" s="3">
         <v>346</v>
       </c>
@@ -54656,7 +54656,7 @@
       <c r="X347" s="4"/>
       <c r="Y347" s="4"/>
     </row>
-    <row r="348" spans="1:25" hidden="1">
+    <row r="348" spans="1:25">
       <c r="A348" s="3">
         <v>347</v>
       </c>
@@ -54726,7 +54726,7 @@
       <c r="X348" s="4"/>
       <c r="Y348" s="4"/>
     </row>
-    <row r="349" spans="1:25">
+    <row r="349" spans="1:25" hidden="1">
       <c r="A349" s="3">
         <v>348</v>
       </c>
@@ -54796,7 +54796,7 @@
       <c r="X349" s="4"/>
       <c r="Y349" s="4"/>
     </row>
-    <row r="350" spans="1:25">
+    <row r="350" spans="1:25" hidden="1">
       <c r="A350" s="3">
         <v>349</v>
       </c>
@@ -54866,7 +54866,7 @@
       <c r="X350" s="4"/>
       <c r="Y350" s="4"/>
     </row>
-    <row r="351" spans="1:25" hidden="1">
+    <row r="351" spans="1:25">
       <c r="A351" s="3">
         <v>350</v>
       </c>
@@ -54932,7 +54932,7 @@
       <c r="X351" s="4"/>
       <c r="Y351" s="4"/>
     </row>
-    <row r="352" spans="1:25" hidden="1">
+    <row r="352" spans="1:25">
       <c r="A352" s="3">
         <v>351</v>
       </c>
@@ -55004,7 +55004,7 @@
       <c r="X352" s="4"/>
       <c r="Y352" s="4"/>
     </row>
-    <row r="353" spans="1:25">
+    <row r="353" spans="1:25" hidden="1">
       <c r="A353" s="3">
         <v>352</v>
       </c>
@@ -55076,7 +55076,7 @@
       <c r="X353" s="4"/>
       <c r="Y353" s="4"/>
     </row>
-    <row r="354" spans="1:25" hidden="1">
+    <row r="354" spans="1:25">
       <c r="A354" s="3">
         <v>353</v>
       </c>
@@ -55140,7 +55140,7 @@
       <c r="X354" s="4"/>
       <c r="Y354" s="4"/>
     </row>
-    <row r="355" spans="1:25" hidden="1">
+    <row r="355" spans="1:25">
       <c r="A355" s="3">
         <v>354</v>
       </c>
@@ -55208,7 +55208,7 @@
       <c r="X355" s="4"/>
       <c r="Y355" s="4"/>
     </row>
-    <row r="356" spans="1:25" hidden="1">
+    <row r="356" spans="1:25">
       <c r="A356" s="3">
         <v>355</v>
       </c>
@@ -55280,7 +55280,7 @@
       <c r="X356" s="4"/>
       <c r="Y356" s="4"/>
     </row>
-    <row r="357" spans="1:25" hidden="1">
+    <row r="357" spans="1:25">
       <c r="A357" s="3">
         <v>356</v>
       </c>
@@ -55350,7 +55350,7 @@
       <c r="X357" s="4"/>
       <c r="Y357" s="4"/>
     </row>
-    <row r="358" spans="1:25" hidden="1">
+    <row r="358" spans="1:25">
       <c r="A358" s="3">
         <v>357</v>
       </c>
@@ -55420,7 +55420,7 @@
       <c r="X358" s="4"/>
       <c r="Y358" s="4"/>
     </row>
-    <row r="359" spans="1:25" hidden="1">
+    <row r="359" spans="1:25">
       <c r="A359" s="3">
         <v>358</v>
       </c>
@@ -55486,7 +55486,7 @@
       <c r="X359" s="4"/>
       <c r="Y359" s="4"/>
     </row>
-    <row r="360" spans="1:25" hidden="1">
+    <row r="360" spans="1:25">
       <c r="A360" s="3">
         <v>359</v>
       </c>
@@ -55556,7 +55556,7 @@
       <c r="X360" s="4"/>
       <c r="Y360" s="4"/>
     </row>
-    <row r="361" spans="1:25" hidden="1">
+    <row r="361" spans="1:25">
       <c r="A361" s="3">
         <v>360</v>
       </c>
@@ -55628,7 +55628,7 @@
       <c r="X361" s="4"/>
       <c r="Y361" s="4"/>
     </row>
-    <row r="362" spans="1:25" hidden="1">
+    <row r="362" spans="1:25">
       <c r="A362" s="3">
         <v>361</v>
       </c>
@@ -55696,7 +55696,7 @@
       <c r="X362" s="4"/>
       <c r="Y362" s="4"/>
     </row>
-    <row r="363" spans="1:25" hidden="1">
+    <row r="363" spans="1:25">
       <c r="A363" s="3">
         <v>362</v>
       </c>
@@ -55762,7 +55762,7 @@
       <c r="X363" s="4"/>
       <c r="Y363" s="4"/>
     </row>
-    <row r="364" spans="1:25" hidden="1">
+    <row r="364" spans="1:25">
       <c r="A364" s="3">
         <v>363</v>
       </c>
@@ -55824,7 +55824,7 @@
       <c r="X364" s="4"/>
       <c r="Y364" s="4"/>
     </row>
-    <row r="365" spans="1:25">
+    <row r="365" spans="1:25" hidden="1">
       <c r="A365" s="3">
         <v>364</v>
       </c>
@@ -55892,7 +55892,7 @@
       </c>
       <c r="Y365" s="4"/>
     </row>
-    <row r="366" spans="1:25">
+    <row r="366" spans="1:25" hidden="1">
       <c r="A366" s="3">
         <v>365</v>
       </c>
@@ -55962,7 +55962,7 @@
       </c>
       <c r="Y366" s="4"/>
     </row>
-    <row r="367" spans="1:25">
+    <row r="367" spans="1:25" hidden="1">
       <c r="A367" s="3">
         <v>366</v>
       </c>
@@ -56030,7 +56030,7 @@
       <c r="X367" s="4"/>
       <c r="Y367" s="4"/>
     </row>
-    <row r="368" spans="1:25">
+    <row r="368" spans="1:25" hidden="1">
       <c r="A368" s="3">
         <v>367</v>
       </c>
@@ -56092,7 +56092,7 @@
       </c>
       <c r="Y368" s="4"/>
     </row>
-    <row r="369" spans="1:25">
+    <row r="369" spans="1:25" hidden="1">
       <c r="A369" s="3">
         <v>368</v>
       </c>
@@ -56154,7 +56154,7 @@
       </c>
       <c r="Y369" s="4"/>
     </row>
-    <row r="370" spans="1:25">
+    <row r="370" spans="1:25" hidden="1">
       <c r="A370" s="3">
         <v>369</v>
       </c>
@@ -56224,7 +56224,7 @@
       </c>
       <c r="Y370" s="4"/>
     </row>
-    <row r="371" spans="1:25">
+    <row r="371" spans="1:25" hidden="1">
       <c r="A371" s="3">
         <v>370</v>
       </c>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="Y371" s="4"/>
     </row>
-    <row r="372" spans="1:25">
+    <row r="372" spans="1:25" hidden="1">
       <c r="A372" s="3">
         <v>371</v>
       </c>
@@ -56366,7 +56366,7 @@
       </c>
       <c r="Y372" s="4"/>
     </row>
-    <row r="373" spans="1:25">
+    <row r="373" spans="1:25" hidden="1">
       <c r="A373" s="3">
         <v>372</v>
       </c>
@@ -56436,7 +56436,7 @@
       </c>
       <c r="Y373" s="4"/>
     </row>
-    <row r="374" spans="1:25">
+    <row r="374" spans="1:25" hidden="1">
       <c r="A374" s="3">
         <v>373</v>
       </c>
@@ -56506,7 +56506,7 @@
       </c>
       <c r="Y374" s="4"/>
     </row>
-    <row r="375" spans="1:25">
+    <row r="375" spans="1:25" hidden="1">
       <c r="A375" s="3">
         <v>374</v>
       </c>
@@ -56576,7 +56576,7 @@
       </c>
       <c r="Y375" s="4"/>
     </row>
-    <row r="376" spans="1:25">
+    <row r="376" spans="1:25" hidden="1">
       <c r="A376" s="3">
         <v>375</v>
       </c>
@@ -56648,7 +56648,7 @@
       </c>
       <c r="Y376" s="4"/>
     </row>
-    <row r="377" spans="1:25">
+    <row r="377" spans="1:25" hidden="1">
       <c r="A377" s="3">
         <v>376</v>
       </c>
@@ -56712,7 +56712,7 @@
       </c>
       <c r="Y377" s="4"/>
     </row>
-    <row r="378" spans="1:25">
+    <row r="378" spans="1:25" hidden="1">
       <c r="A378" s="3">
         <v>377</v>
       </c>
@@ -56786,7 +56786,7 @@
       </c>
       <c r="Y378" s="4"/>
     </row>
-    <row r="379" spans="1:25" hidden="1">
+    <row r="379" spans="1:25">
       <c r="A379" s="3">
         <v>378</v>
       </c>
@@ -56856,7 +56856,7 @@
       <c r="X379" s="18"/>
       <c r="Y379" s="4"/>
     </row>
-    <row r="380" spans="1:25" hidden="1">
+    <row r="380" spans="1:25">
       <c r="A380" s="3">
         <v>379</v>
       </c>
@@ -56926,7 +56926,7 @@
       <c r="X380" s="4"/>
       <c r="Y380" s="4"/>
     </row>
-    <row r="381" spans="1:25" hidden="1">
+    <row r="381" spans="1:25">
       <c r="A381" s="3">
         <v>380</v>
       </c>
@@ -56992,7 +56992,7 @@
       <c r="X381" s="4"/>
       <c r="Y381" s="4"/>
     </row>
-    <row r="382" spans="1:25" hidden="1">
+    <row r="382" spans="1:25">
       <c r="A382" s="3">
         <v>381</v>
       </c>
@@ -57064,7 +57064,7 @@
       <c r="X382" s="4"/>
       <c r="Y382" s="4"/>
     </row>
-    <row r="383" spans="1:25" hidden="1">
+    <row r="383" spans="1:25">
       <c r="A383" s="3">
         <v>382</v>
       </c>
@@ -57126,7 +57126,7 @@
       <c r="X383" s="4"/>
       <c r="Y383" s="4"/>
     </row>
-    <row r="384" spans="1:25" hidden="1">
+    <row r="384" spans="1:25">
       <c r="A384" s="3">
         <v>383</v>
       </c>
@@ -57190,7 +57190,7 @@
       <c r="X384" s="4"/>
       <c r="Y384" s="4"/>
     </row>
-    <row r="385" spans="1:25" hidden="1">
+    <row r="385" spans="1:25">
       <c r="A385" s="3">
         <v>384</v>
       </c>
@@ -57254,7 +57254,7 @@
       <c r="X385" s="4"/>
       <c r="Y385" s="4"/>
     </row>
-    <row r="386" spans="1:25" hidden="1">
+    <row r="386" spans="1:25">
       <c r="A386" s="3">
         <v>385</v>
       </c>
@@ -57320,7 +57320,7 @@
       <c r="X386" s="18"/>
       <c r="Y386" s="4"/>
     </row>
-    <row r="387" spans="1:25">
+    <row r="387" spans="1:25" hidden="1">
       <c r="A387" s="3">
         <v>386</v>
       </c>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="Y387" s="4"/>
     </row>
-    <row r="388" spans="1:25">
+    <row r="388" spans="1:25" hidden="1">
       <c r="A388" s="3">
         <v>387</v>
       </c>
@@ -57456,7 +57456,7 @@
       </c>
       <c r="Y388" s="4"/>
     </row>
-    <row r="389" spans="1:25">
+    <row r="389" spans="1:25" hidden="1">
       <c r="A389" s="3">
         <v>388</v>
       </c>
@@ -57524,7 +57524,7 @@
       </c>
       <c r="Y389" s="4"/>
     </row>
-    <row r="390" spans="1:25">
+    <row r="390" spans="1:25" hidden="1">
       <c r="A390" s="3">
         <v>389</v>
       </c>
@@ -57586,7 +57586,7 @@
       <c r="X390" s="4"/>
       <c r="Y390" s="4"/>
     </row>
-    <row r="391" spans="1:25">
+    <row r="391" spans="1:25" hidden="1">
       <c r="A391" s="3">
         <v>390</v>
       </c>
@@ -57654,7 +57654,7 @@
       </c>
       <c r="Y391" s="4"/>
     </row>
-    <row r="392" spans="1:25">
+    <row r="392" spans="1:25" hidden="1">
       <c r="A392" s="3">
         <v>391</v>
       </c>
@@ -57720,7 +57720,7 @@
       </c>
       <c r="Y392" s="4"/>
     </row>
-    <row r="393" spans="1:25" hidden="1">
+    <row r="393" spans="1:25">
       <c r="A393" s="3">
         <v>392</v>
       </c>
@@ -57778,7 +57778,7 @@
       </c>
       <c r="Y393" s="4"/>
     </row>
-    <row r="394" spans="1:25">
+    <row r="394" spans="1:25" hidden="1">
       <c r="A394" s="3">
         <v>393</v>
       </c>
@@ -57840,7 +57840,7 @@
       <c r="X394" s="3"/>
       <c r="Y394" s="4"/>
     </row>
-    <row r="395" spans="1:25">
+    <row r="395" spans="1:25" hidden="1">
       <c r="A395" s="3">
         <v>394</v>
       </c>
@@ -57906,7 +57906,7 @@
       </c>
       <c r="Y395" s="4"/>
     </row>
-    <row r="396" spans="1:25">
+    <row r="396" spans="1:25" hidden="1">
       <c r="A396" s="3">
         <v>395</v>
       </c>
@@ -57970,7 +57970,7 @@
       <c r="X396" s="28"/>
       <c r="Y396" s="4"/>
     </row>
-    <row r="397" spans="1:25" hidden="1">
+    <row r="397" spans="1:25">
       <c r="A397" s="3">
         <v>396</v>
       </c>
@@ -58036,7 +58036,7 @@
       <c r="X397" s="28"/>
       <c r="Y397" s="4"/>
     </row>
-    <row r="398" spans="1:25" hidden="1">
+    <row r="398" spans="1:25">
       <c r="A398" s="3">
         <v>397</v>
       </c>
@@ -58098,7 +58098,7 @@
       <c r="X398" s="28"/>
       <c r="Y398" s="4"/>
     </row>
-    <row r="399" spans="1:25" hidden="1">
+    <row r="399" spans="1:25">
       <c r="A399" s="3">
         <v>398</v>
       </c>
@@ -58164,7 +58164,7 @@
       <c r="X399" s="28"/>
       <c r="Y399" s="4"/>
     </row>
-    <row r="400" spans="1:25" hidden="1">
+    <row r="400" spans="1:25">
       <c r="A400" s="3">
         <v>399</v>
       </c>
@@ -58234,7 +58234,7 @@
       <c r="X400" s="28"/>
       <c r="Y400" s="4"/>
     </row>
-    <row r="401" spans="1:25" hidden="1">
+    <row r="401" spans="1:25">
       <c r="A401" s="3">
         <v>400</v>
       </c>
@@ -58298,7 +58298,7 @@
       <c r="X401" s="28"/>
       <c r="Y401" s="4"/>
     </row>
-    <row r="402" spans="1:25" hidden="1">
+    <row r="402" spans="1:25">
       <c r="A402" s="3">
         <v>401</v>
       </c>
@@ -58360,7 +58360,7 @@
       <c r="X402" s="28"/>
       <c r="Y402" s="4"/>
     </row>
-    <row r="403" spans="1:25" hidden="1">
+    <row r="403" spans="1:25">
       <c r="A403" s="3">
         <v>402</v>
       </c>
@@ -58424,7 +58424,7 @@
       <c r="X403" s="28"/>
       <c r="Y403" s="4"/>
     </row>
-    <row r="404" spans="1:25" hidden="1">
+    <row r="404" spans="1:25">
       <c r="A404" s="3">
         <v>403</v>
       </c>
@@ -58486,7 +58486,7 @@
       <c r="X404" s="29"/>
       <c r="Y404" s="4"/>
     </row>
-    <row r="405" spans="1:25" hidden="1">
+    <row r="405" spans="1:25">
       <c r="A405" s="3">
         <v>404</v>
       </c>
@@ -58548,7 +58548,7 @@
       <c r="X405" s="3"/>
       <c r="Y405" s="4"/>
     </row>
-    <row r="406" spans="1:25">
+    <row r="406" spans="1:25" hidden="1">
       <c r="A406" s="3">
         <v>405</v>
       </c>
@@ -58614,7 +58614,7 @@
       </c>
       <c r="Y406" s="4"/>
     </row>
-    <row r="407" spans="1:25">
+    <row r="407" spans="1:25" hidden="1">
       <c r="A407" s="3">
         <v>406</v>
       </c>
@@ -58680,7 +58680,7 @@
       </c>
       <c r="Y407" s="4"/>
     </row>
-    <row r="408" spans="1:25">
+    <row r="408" spans="1:25" hidden="1">
       <c r="A408" s="3">
         <v>407</v>
       </c>
@@ -58748,7 +58748,7 @@
       </c>
       <c r="Y408" s="4"/>
     </row>
-    <row r="409" spans="1:25">
+    <row r="409" spans="1:25" hidden="1">
       <c r="A409" s="3">
         <v>408</v>
       </c>
@@ -58816,7 +58816,7 @@
       </c>
       <c r="Y409" s="4"/>
     </row>
-    <row r="410" spans="1:25">
+    <row r="410" spans="1:25" hidden="1">
       <c r="A410" s="3">
         <v>409</v>
       </c>
@@ -58884,7 +58884,7 @@
       </c>
       <c r="Y410" s="4"/>
     </row>
-    <row r="411" spans="1:25">
+    <row r="411" spans="1:25" hidden="1">
       <c r="A411" s="3">
         <v>410</v>
       </c>
@@ -58950,7 +58950,7 @@
       </c>
       <c r="Y411" s="4"/>
     </row>
-    <row r="412" spans="1:25">
+    <row r="412" spans="1:25" hidden="1">
       <c r="A412" s="3">
         <v>411</v>
       </c>
@@ -59016,7 +59016,7 @@
       </c>
       <c r="Y412" s="4"/>
     </row>
-    <row r="413" spans="1:25">
+    <row r="413" spans="1:25" hidden="1">
       <c r="A413" s="3">
         <v>412</v>
       </c>
@@ -59084,7 +59084,7 @@
       </c>
       <c r="Y413" s="4"/>
     </row>
-    <row r="414" spans="1:25">
+    <row r="414" spans="1:25" hidden="1">
       <c r="A414" s="3">
         <v>413</v>
       </c>
@@ -59148,7 +59148,7 @@
       </c>
       <c r="Y414" s="4"/>
     </row>
-    <row r="415" spans="1:25">
+    <row r="415" spans="1:25" hidden="1">
       <c r="A415" s="3">
         <v>414</v>
       </c>
@@ -59208,7 +59208,7 @@
       <c r="X415" s="3"/>
       <c r="Y415" s="4"/>
     </row>
-    <row r="416" spans="1:25">
+    <row r="416" spans="1:25" hidden="1">
       <c r="A416" s="3">
         <v>415</v>
       </c>
@@ -59276,7 +59276,7 @@
       </c>
       <c r="Y416" s="4"/>
     </row>
-    <row r="417" spans="1:25" hidden="1">
+    <row r="417" spans="1:25">
       <c r="A417" s="3">
         <v>416</v>
       </c>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="Y417" s="4"/>
     </row>
-    <row r="418" spans="1:25" hidden="1">
+    <row r="418" spans="1:25">
       <c r="A418" s="3">
         <v>417</v>
       </c>
@@ -59418,7 +59418,7 @@
       </c>
       <c r="Y418" s="4"/>
     </row>
-    <row r="419" spans="1:25">
+    <row r="419" spans="1:25" hidden="1">
       <c r="A419" s="3">
         <v>418</v>
       </c>
@@ -59486,7 +59486,7 @@
       <c r="X419" s="18"/>
       <c r="Y419" s="4"/>
     </row>
-    <row r="420" spans="1:25">
+    <row r="420" spans="1:25" hidden="1">
       <c r="A420" s="3">
         <v>419</v>
       </c>
@@ -59554,7 +59554,7 @@
       </c>
       <c r="Y420" s="4"/>
     </row>
-    <row r="421" spans="1:25">
+    <row r="421" spans="1:25" hidden="1">
       <c r="A421" s="3">
         <v>420</v>
       </c>
@@ -59624,7 +59624,7 @@
       </c>
       <c r="Y421" s="4"/>
     </row>
-    <row r="422" spans="1:25">
+    <row r="422" spans="1:25" hidden="1">
       <c r="A422" s="3">
         <v>421</v>
       </c>
@@ -59694,7 +59694,7 @@
       </c>
       <c r="Y422" s="4"/>
     </row>
-    <row r="423" spans="1:25">
+    <row r="423" spans="1:25" hidden="1">
       <c r="A423" s="3">
         <v>422</v>
       </c>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="Y423" s="4"/>
     </row>
-    <row r="424" spans="1:25">
+    <row r="424" spans="1:25" hidden="1">
       <c r="A424" s="3">
         <v>423</v>
       </c>
@@ -59834,7 +59834,7 @@
       </c>
       <c r="Y424" s="4"/>
     </row>
-    <row r="425" spans="1:25">
+    <row r="425" spans="1:25" hidden="1">
       <c r="A425" s="3">
         <v>424</v>
       </c>
@@ -59904,7 +59904,7 @@
       </c>
       <c r="Y425" s="4"/>
     </row>
-    <row r="426" spans="1:25">
+    <row r="426" spans="1:25" hidden="1">
       <c r="A426" s="3">
         <v>425</v>
       </c>
@@ -59974,7 +59974,7 @@
       </c>
       <c r="Y426" s="4"/>
     </row>
-    <row r="427" spans="1:25">
+    <row r="427" spans="1:25" hidden="1">
       <c r="A427" s="3">
         <v>426</v>
       </c>
@@ -60044,7 +60044,7 @@
       </c>
       <c r="Y427" s="4"/>
     </row>
-    <row r="428" spans="1:25">
+    <row r="428" spans="1:25" hidden="1">
       <c r="A428" s="3">
         <v>427</v>
       </c>
@@ -60114,7 +60114,7 @@
       </c>
       <c r="Y428" s="4"/>
     </row>
-    <row r="429" spans="1:25">
+    <row r="429" spans="1:25" hidden="1">
       <c r="A429" s="3">
         <v>428</v>
       </c>
@@ -60184,7 +60184,7 @@
       </c>
       <c r="Y429" s="4"/>
     </row>
-    <row r="430" spans="1:25" hidden="1">
+    <row r="430" spans="1:25">
       <c r="A430" s="3">
         <v>429</v>
       </c>
@@ -60246,7 +60246,7 @@
       <c r="X430" s="31"/>
       <c r="Y430" s="4"/>
     </row>
-    <row r="431" spans="1:25" hidden="1">
+    <row r="431" spans="1:25">
       <c r="A431" s="3">
         <v>430</v>
       </c>
@@ -60314,7 +60314,7 @@
       </c>
       <c r="Y431" s="4"/>
     </row>
-    <row r="432" spans="1:25">
+    <row r="432" spans="1:25" hidden="1">
       <c r="A432" s="3">
         <v>431</v>
       </c>
@@ -60380,7 +60380,7 @@
       <c r="X432" s="4"/>
       <c r="Y432" s="4"/>
     </row>
-    <row r="433" spans="1:25">
+    <row r="433" spans="1:25" hidden="1">
       <c r="A433" s="3">
         <v>432</v>
       </c>
@@ -60442,7 +60442,7 @@
       <c r="X433" s="4"/>
       <c r="Y433" s="4"/>
     </row>
-    <row r="434" spans="1:25" hidden="1">
+    <row r="434" spans="1:25">
       <c r="A434" s="3">
         <v>433</v>
       </c>
@@ -60504,7 +60504,7 @@
       <c r="X434" s="4"/>
       <c r="Y434" s="4"/>
     </row>
-    <row r="435" spans="1:25">
+    <row r="435" spans="1:25" hidden="1">
       <c r="A435" s="3">
         <v>434</v>
       </c>
@@ -60558,7 +60558,7 @@
       <c r="X435" s="4"/>
       <c r="Y435" s="4"/>
     </row>
-    <row r="436" spans="1:25">
+    <row r="436" spans="1:25" hidden="1">
       <c r="A436" s="3">
         <v>435</v>
       </c>
@@ -60622,7 +60622,7 @@
       <c r="X436" s="4"/>
       <c r="Y436" s="4"/>
     </row>
-    <row r="437" spans="1:25">
+    <row r="437" spans="1:25" hidden="1">
       <c r="A437" s="3">
         <v>436</v>
       </c>
@@ -60686,7 +60686,7 @@
       <c r="X437" s="4"/>
       <c r="Y437" s="4"/>
     </row>
-    <row r="438" spans="1:25">
+    <row r="438" spans="1:25" hidden="1">
       <c r="A438" s="3">
         <v>437</v>
       </c>
@@ -60750,7 +60750,7 @@
       <c r="X438" s="4"/>
       <c r="Y438" s="4"/>
     </row>
-    <row r="439" spans="1:25">
+    <row r="439" spans="1:25" hidden="1">
       <c r="A439" s="3">
         <v>438</v>
       </c>
@@ -60814,7 +60814,7 @@
       <c r="X439" s="4"/>
       <c r="Y439" s="4"/>
     </row>
-    <row r="440" spans="1:25">
+    <row r="440" spans="1:25" hidden="1">
       <c r="A440" s="3">
         <v>439</v>
       </c>
@@ -60878,7 +60878,7 @@
       <c r="X440" s="4"/>
       <c r="Y440" s="4"/>
     </row>
-    <row r="441" spans="1:25">
+    <row r="441" spans="1:25" hidden="1">
       <c r="A441" s="3">
         <v>440</v>
       </c>
@@ -60942,7 +60942,7 @@
       <c r="X441" s="4"/>
       <c r="Y441" s="4"/>
     </row>
-    <row r="442" spans="1:25">
+    <row r="442" spans="1:25" hidden="1">
       <c r="A442" s="3">
         <v>441</v>
       </c>
@@ -61006,7 +61006,7 @@
       <c r="X442" s="4"/>
       <c r="Y442" s="4"/>
     </row>
-    <row r="443" spans="1:25">
+    <row r="443" spans="1:25" hidden="1">
       <c r="A443" s="3">
         <v>442</v>
       </c>
@@ -61070,7 +61070,7 @@
       <c r="X443" s="18"/>
       <c r="Y443" s="4"/>
     </row>
-    <row r="444" spans="1:25">
+    <row r="444" spans="1:25" hidden="1">
       <c r="A444" s="3">
         <v>443</v>
       </c>
@@ -61138,7 +61138,7 @@
       </c>
       <c r="Y444" s="4"/>
     </row>
-    <row r="445" spans="1:25">
+    <row r="445" spans="1:25" hidden="1">
       <c r="A445" s="3">
         <v>444</v>
       </c>
@@ -61204,7 +61204,7 @@
       <c r="X445" s="18"/>
       <c r="Y445" s="4"/>
     </row>
-    <row r="446" spans="1:25">
+    <row r="446" spans="1:25" hidden="1">
       <c r="A446" s="3">
         <v>445</v>
       </c>
@@ -61270,7 +61270,7 @@
       </c>
       <c r="Y446" s="4"/>
     </row>
-    <row r="447" spans="1:25" hidden="1">
+    <row r="447" spans="1:25">
       <c r="A447" s="3">
         <v>446</v>
       </c>
@@ -61336,7 +61336,7 @@
       <c r="X447" s="3"/>
       <c r="Y447" s="4"/>
     </row>
-    <row r="448" spans="1:25" hidden="1">
+    <row r="448" spans="1:25">
       <c r="A448" s="3">
         <v>447</v>
       </c>
@@ -61406,7 +61406,7 @@
       </c>
       <c r="Y448" s="4"/>
     </row>
-    <row r="449" spans="1:25" hidden="1">
+    <row r="449" spans="1:25">
       <c r="A449" s="3">
         <v>448</v>
       </c>
@@ -61470,7 +61470,7 @@
       <c r="X449" s="3"/>
       <c r="Y449" s="4"/>
     </row>
-    <row r="450" spans="1:25" hidden="1">
+    <row r="450" spans="1:25">
       <c r="A450" s="3">
         <v>449</v>
       </c>
@@ -61534,7 +61534,7 @@
       <c r="X450" s="3"/>
       <c r="Y450" s="4"/>
     </row>
-    <row r="451" spans="1:25">
+    <row r="451" spans="1:25" hidden="1">
       <c r="A451" s="3">
         <v>451</v>
       </c>
@@ -61600,7 +61600,7 @@
       <c r="X451" s="3"/>
       <c r="Y451" s="4"/>
     </row>
-    <row r="452" spans="1:25">
+    <row r="452" spans="1:25" hidden="1">
       <c r="A452" s="3">
         <v>452</v>
       </c>
@@ -61668,7 +61668,7 @@
       </c>
       <c r="Y452" s="4"/>
     </row>
-    <row r="453" spans="1:25">
+    <row r="453" spans="1:25" hidden="1">
       <c r="A453" s="3">
         <v>453</v>
       </c>
@@ -61724,7 +61724,7 @@
       <c r="X453" s="3"/>
       <c r="Y453" s="4"/>
     </row>
-    <row r="454" spans="1:25">
+    <row r="454" spans="1:25" hidden="1">
       <c r="A454" s="3">
         <v>454</v>
       </c>
@@ -61792,7 +61792,7 @@
       </c>
       <c r="Y454" s="4"/>
     </row>
-    <row r="455" spans="1:25">
+    <row r="455" spans="1:25" hidden="1">
       <c r="A455" s="3">
         <v>455</v>
       </c>
@@ -61854,7 +61854,7 @@
       </c>
       <c r="Y455" s="4"/>
     </row>
-    <row r="456" spans="1:25">
+    <row r="456" spans="1:25" hidden="1">
       <c r="A456" s="3">
         <v>456</v>
       </c>
@@ -61918,7 +61918,7 @@
       </c>
       <c r="Y456" s="4"/>
     </row>
-    <row r="457" spans="1:25">
+    <row r="457" spans="1:25" hidden="1">
       <c r="A457" s="3">
         <v>457</v>
       </c>
@@ -61984,7 +61984,7 @@
       </c>
       <c r="Y457" s="4"/>
     </row>
-    <row r="458" spans="1:25">
+    <row r="458" spans="1:25" hidden="1">
       <c r="A458" s="3">
         <v>458</v>
       </c>
@@ -62048,7 +62048,7 @@
       </c>
       <c r="Y458" s="4"/>
     </row>
-    <row r="459" spans="1:25">
+    <row r="459" spans="1:25" hidden="1">
       <c r="A459" s="3">
         <v>459</v>
       </c>
@@ -62116,7 +62116,7 @@
       </c>
       <c r="Y459" s="4"/>
     </row>
-    <row r="460" spans="1:25">
+    <row r="460" spans="1:25" hidden="1">
       <c r="A460" s="3">
         <v>460</v>
       </c>
@@ -62180,7 +62180,7 @@
       </c>
       <c r="Y460" s="4"/>
     </row>
-    <row r="461" spans="1:25">
+    <row r="461" spans="1:25" hidden="1">
       <c r="A461" s="3">
         <v>461</v>
       </c>
@@ -62246,7 +62246,7 @@
       <c r="X461" s="18"/>
       <c r="Y461" s="4"/>
     </row>
-    <row r="462" spans="1:25">
+    <row r="462" spans="1:25" hidden="1">
       <c r="A462" s="3">
         <v>462</v>
       </c>
@@ -62316,7 +62316,7 @@
       <c r="X462" s="18"/>
       <c r="Y462" s="4"/>
     </row>
-    <row r="463" spans="1:25">
+    <row r="463" spans="1:25" hidden="1">
       <c r="A463" s="3">
         <v>463</v>
       </c>
@@ -62384,7 +62384,7 @@
       <c r="X463" s="18"/>
       <c r="Y463" s="4"/>
     </row>
-    <row r="464" spans="1:25">
+    <row r="464" spans="1:25" hidden="1">
       <c r="A464" s="3">
         <v>464</v>
       </c>
@@ -62452,7 +62452,7 @@
       <c r="X464" s="4"/>
       <c r="Y464" s="4"/>
     </row>
-    <row r="465" spans="1:25" ht="12.75" customHeight="1">
+    <row r="465" spans="1:25" ht="12.75" hidden="1" customHeight="1">
       <c r="A465" s="3">
         <v>465</v>
       </c>
@@ -62516,7 +62516,7 @@
       </c>
       <c r="Y465" s="4"/>
     </row>
-    <row r="466" spans="1:25">
+    <row r="466" spans="1:25" hidden="1">
       <c r="A466" s="3">
         <v>466</v>
       </c>
@@ -62584,7 +62584,7 @@
       </c>
       <c r="Y466" s="4"/>
     </row>
-    <row r="467" spans="1:25">
+    <row r="467" spans="1:25" hidden="1">
       <c r="A467" s="3">
         <v>467</v>
       </c>
@@ -62654,7 +62654,7 @@
       </c>
       <c r="Y467" s="4"/>
     </row>
-    <row r="468" spans="1:25">
+    <row r="468" spans="1:25" hidden="1">
       <c r="A468" s="3">
         <v>468</v>
       </c>
@@ -62724,7 +62724,7 @@
       </c>
       <c r="Y468" s="4"/>
     </row>
-    <row r="469" spans="1:25">
+    <row r="469" spans="1:25" hidden="1">
       <c r="A469" s="3">
         <v>469</v>
       </c>
@@ -62794,7 +62794,7 @@
       </c>
       <c r="Y469" s="4"/>
     </row>
-    <row r="470" spans="1:25">
+    <row r="470" spans="1:25" hidden="1">
       <c r="A470" s="3">
         <v>470</v>
       </c>
@@ -62858,7 +62858,7 @@
       <c r="X470" s="18"/>
       <c r="Y470" s="4"/>
     </row>
-    <row r="471" spans="1:25">
+    <row r="471" spans="1:25" hidden="1">
       <c r="A471" s="3">
         <v>471</v>
       </c>
@@ -62924,7 +62924,7 @@
       </c>
       <c r="Y471" s="4"/>
     </row>
-    <row r="472" spans="1:25">
+    <row r="472" spans="1:25" hidden="1">
       <c r="A472" s="3">
         <v>472</v>
       </c>
@@ -62988,7 +62988,7 @@
       </c>
       <c r="Y472" s="4"/>
     </row>
-    <row r="473" spans="1:25" hidden="1">
+    <row r="473" spans="1:25">
       <c r="A473" s="3">
         <v>473</v>
       </c>
@@ -63060,7 +63060,7 @@
       </c>
       <c r="Y473" s="4"/>
     </row>
-    <row r="474" spans="1:25">
+    <row r="474" spans="1:25" hidden="1">
       <c r="A474" s="3">
         <v>474</v>
       </c>
@@ -63130,7 +63130,7 @@
       </c>
       <c r="Y474" s="4"/>
     </row>
-    <row r="475" spans="1:25">
+    <row r="475" spans="1:25" hidden="1">
       <c r="A475" s="3">
         <v>475</v>
       </c>
@@ -63196,7 +63196,7 @@
       </c>
       <c r="Y475" s="4"/>
     </row>
-    <row r="476" spans="1:25">
+    <row r="476" spans="1:25" hidden="1">
       <c r="A476" s="3">
         <v>476</v>
       </c>
@@ -63266,7 +63266,7 @@
       </c>
       <c r="Y476" s="4"/>
     </row>
-    <row r="477" spans="1:25">
+    <row r="477" spans="1:25" hidden="1">
       <c r="A477" s="3">
         <v>477</v>
       </c>
@@ -63334,7 +63334,7 @@
       </c>
       <c r="Y477" s="4"/>
     </row>
-    <row r="478" spans="1:25">
+    <row r="478" spans="1:25" hidden="1">
       <c r="A478" s="3">
         <v>478</v>
       </c>
@@ -63406,7 +63406,7 @@
       </c>
       <c r="Y478" s="4"/>
     </row>
-    <row r="479" spans="1:25" hidden="1">
+    <row r="479" spans="1:25">
       <c r="A479" s="3">
         <v>479</v>
       </c>
@@ -63478,7 +63478,7 @@
       </c>
       <c r="Y479" s="4"/>
     </row>
-    <row r="480" spans="1:25" hidden="1">
+    <row r="480" spans="1:25">
       <c r="A480" s="3">
         <v>480</v>
       </c>
@@ -63544,7 +63544,7 @@
       <c r="X480" s="57"/>
       <c r="Y480" s="18"/>
     </row>
-    <row r="481" spans="1:25">
+    <row r="481" spans="1:25" hidden="1">
       <c r="A481" s="3">
         <v>481</v>
       </c>
@@ -63614,7 +63614,7 @@
       </c>
       <c r="Y481" s="4"/>
     </row>
-    <row r="482" spans="1:25">
+    <row r="482" spans="1:25" hidden="1">
       <c r="A482" s="3">
         <v>482</v>
       </c>
@@ -63682,7 +63682,7 @@
       </c>
       <c r="Y482" s="4"/>
     </row>
-    <row r="483" spans="1:25">
+    <row r="483" spans="1:25" hidden="1">
       <c r="A483" s="3">
         <v>483</v>
       </c>
@@ -63748,7 +63748,7 @@
       </c>
       <c r="Y483" s="4"/>
     </row>
-    <row r="484" spans="1:25">
+    <row r="484" spans="1:25" hidden="1">
       <c r="A484" s="3">
         <v>484</v>
       </c>
@@ -63816,7 +63816,7 @@
       <c r="X484" s="3"/>
       <c r="Y484" s="4"/>
     </row>
-    <row r="485" spans="1:25">
+    <row r="485" spans="1:25" hidden="1">
       <c r="A485" s="3">
         <v>485</v>
       </c>
@@ -63882,7 +63882,7 @@
       </c>
       <c r="Y485" s="4"/>
     </row>
-    <row r="486" spans="1:25">
+    <row r="486" spans="1:25" hidden="1">
       <c r="A486" s="3">
         <v>486</v>
       </c>
@@ -63952,7 +63952,7 @@
       </c>
       <c r="Y486" s="4"/>
     </row>
-    <row r="487" spans="1:25">
+    <row r="487" spans="1:25" hidden="1">
       <c r="A487" s="3">
         <v>487</v>
       </c>
@@ -64020,7 +64020,7 @@
       </c>
       <c r="Y487" s="4"/>
     </row>
-    <row r="488" spans="1:25">
+    <row r="488" spans="1:25" hidden="1">
       <c r="A488" s="3">
         <v>488</v>
       </c>
@@ -64086,7 +64086,7 @@
       </c>
       <c r="Y488" s="4"/>
     </row>
-    <row r="489" spans="1:25">
+    <row r="489" spans="1:25" hidden="1">
       <c r="A489" s="3">
         <v>489</v>
       </c>
@@ -64152,7 +64152,7 @@
       </c>
       <c r="Y489" s="4"/>
     </row>
-    <row r="490" spans="1:25">
+    <row r="490" spans="1:25" hidden="1">
       <c r="A490" s="3">
         <v>490</v>
       </c>
@@ -64222,7 +64222,7 @@
       </c>
       <c r="Y490" s="18"/>
     </row>
-    <row r="491" spans="1:25">
+    <row r="491" spans="1:25" hidden="1">
       <c r="A491" s="3">
         <v>491</v>
       </c>
@@ -64290,7 +64290,7 @@
       </c>
       <c r="Y491" s="4"/>
     </row>
-    <row r="492" spans="1:25">
+    <row r="492" spans="1:25" hidden="1">
       <c r="A492" s="3">
         <v>492</v>
       </c>
@@ -64358,7 +64358,7 @@
       </c>
       <c r="Y492" s="4"/>
     </row>
-    <row r="493" spans="1:25">
+    <row r="493" spans="1:25" hidden="1">
       <c r="A493" s="3">
         <v>493</v>
       </c>
@@ -64426,7 +64426,7 @@
       </c>
       <c r="Y493" s="4"/>
     </row>
-    <row r="494" spans="1:25">
+    <row r="494" spans="1:25" hidden="1">
       <c r="A494" s="3">
         <v>494</v>
       </c>
@@ -64494,7 +64494,7 @@
       </c>
       <c r="Y494" s="4"/>
     </row>
-    <row r="495" spans="1:25">
+    <row r="495" spans="1:25" hidden="1">
       <c r="A495" s="3">
         <v>495</v>
       </c>
@@ -64562,7 +64562,7 @@
       </c>
       <c r="Y495" s="18"/>
     </row>
-    <row r="496" spans="1:25">
+    <row r="496" spans="1:25" hidden="1">
       <c r="A496" s="3">
         <v>496</v>
       </c>
@@ -64626,7 +64626,7 @@
       </c>
       <c r="Y496" s="18"/>
     </row>
-    <row r="497" spans="1:25" hidden="1">
+    <row r="497" spans="1:25">
       <c r="A497" s="3">
         <v>497</v>
       </c>
@@ -64696,7 +64696,7 @@
       </c>
       <c r="Y497" s="4"/>
     </row>
-    <row r="498" spans="1:25" hidden="1">
+    <row r="498" spans="1:25">
       <c r="A498" s="3">
         <v>498</v>
       </c>
@@ -64768,7 +64768,7 @@
       </c>
       <c r="Y498" s="4"/>
     </row>
-    <row r="499" spans="1:25" hidden="1">
+    <row r="499" spans="1:25">
       <c r="A499" s="3">
         <v>499</v>
       </c>
@@ -64840,7 +64840,7 @@
       </c>
       <c r="Y499" s="4"/>
     </row>
-    <row r="500" spans="1:25" hidden="1">
+    <row r="500" spans="1:25">
       <c r="A500" s="3">
         <v>500</v>
       </c>
@@ -64912,7 +64912,7 @@
       </c>
       <c r="Y500" s="18"/>
     </row>
-    <row r="501" spans="1:25">
+    <row r="501" spans="1:25" hidden="1">
       <c r="A501" s="3">
         <v>501</v>
       </c>
